--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125193041</v>
+        <v>125194671</v>
       </c>
       <c r="B3" t="n">
         <v>57513</v>
@@ -832,14 +832,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>595982</v>
+        <v>596069</v>
       </c>
       <c r="R3" t="n">
-        <v>6925883</v>
+        <v>6925880</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Väldigt många.</t>
+          <t>Ringhack av tretåig hackspett på Tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,22 +901,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125195720</v>
+        <v>125194517</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,42 +925,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>90</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596021</v>
+        <v>596060</v>
       </c>
       <c r="R4" t="n">
-        <v>6925959</v>
+        <v>6925896</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,19 +1018,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125194671</v>
+        <v>125193041</v>
       </c>
       <c r="B5" t="n">
         <v>57513</v>
@@ -1070,14 +1071,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596069</v>
+        <v>595982</v>
       </c>
       <c r="R5" t="n">
-        <v>6925880</v>
+        <v>6925883</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,12 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall.</t>
+          <t>Ringhack på tall.  Väldigt många.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,22 +1140,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125194517</v>
+        <v>125195720</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,43 +1164,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>90</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596060</v>
+        <v>596021</v>
       </c>
       <c r="R6" t="n">
-        <v>6925896</v>
+        <v>6925959</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,12 +1256,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -2689,10 +2689,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125194304</v>
+        <v>125192270</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2705,39 +2705,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596074</v>
+        <v>596164</v>
       </c>
       <c r="R19" t="n">
-        <v>6925862</v>
+        <v>6925821</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2769,7 +2764,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2779,12 +2774,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2799,22 +2789,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125192270</v>
+        <v>125194304</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2827,34 +2817,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596164</v>
+        <v>596074</v>
       </c>
       <c r="R20" t="n">
-        <v>6925821</v>
+        <v>6925862</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2886,7 +2881,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2896,7 +2891,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2911,12 +2911,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3754,10 +3754,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125194116</v>
+        <v>125191651</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3766,30 +3766,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3798,10 +3799,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596053</v>
+        <v>596135</v>
       </c>
       <c r="R28" t="n">
-        <v>6925860</v>
+        <v>6925799</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3833,7 +3834,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3843,7 +3844,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3870,10 +3876,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125191651</v>
+        <v>125195016</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3886,16 +3892,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3911,14 +3917,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596135</v>
+        <v>596057</v>
       </c>
       <c r="R29" t="n">
-        <v>6925799</v>
+        <v>6925928</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3950,7 +3956,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3960,12 +3966,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3980,22 +3981,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125195016</v>
+        <v>125194116</v>
       </c>
       <c r="B30" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4004,43 +4005,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596057</v>
+        <v>596053</v>
       </c>
       <c r="R30" t="n">
-        <v>6925928</v>
+        <v>6925860</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4072,7 +4072,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4097,12 +4097,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -2689,10 +2689,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125192270</v>
+        <v>125194304</v>
       </c>
       <c r="B19" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2705,34 +2705,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596164</v>
+        <v>596074</v>
       </c>
       <c r="R19" t="n">
-        <v>6925821</v>
+        <v>6925862</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2764,7 +2769,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2774,7 +2779,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2789,22 +2799,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125194304</v>
+        <v>125192270</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2817,39 +2827,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596074</v>
+        <v>596164</v>
       </c>
       <c r="R20" t="n">
-        <v>6925862</v>
+        <v>6925821</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2881,7 +2886,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2891,12 +2896,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2911,22 +2911,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125193970</v>
+        <v>125195800</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2935,31 +2935,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2968,10 +2967,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596053</v>
+        <v>596030</v>
       </c>
       <c r="R21" t="n">
-        <v>6925860</v>
+        <v>6925941</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3003,7 +3002,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3013,12 +3012,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3045,10 +3039,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125195800</v>
+        <v>125193970</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3057,30 +3051,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3089,10 +3084,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596030</v>
+        <v>596053</v>
       </c>
       <c r="R22" t="n">
-        <v>6925941</v>
+        <v>6925860</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3124,7 +3119,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3134,7 +3129,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3754,10 +3754,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125191651</v>
+        <v>125195016</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3770,16 +3770,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3795,14 +3795,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596135</v>
+        <v>596057</v>
       </c>
       <c r="R28" t="n">
-        <v>6925799</v>
+        <v>6925928</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3844,12 +3844,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3864,22 +3859,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125195016</v>
+        <v>125191651</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3892,16 +3887,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3917,14 +3912,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596057</v>
+        <v>596135</v>
       </c>
       <c r="R29" t="n">
-        <v>6925928</v>
+        <v>6925799</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3956,7 +3951,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3966,7 +3961,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3981,12 +3981,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125194492</v>
+        <v>125195016</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596063</v>
+        <v>596057</v>
       </c>
       <c r="R2" t="n">
-        <v>6925899</v>
+        <v>6925928</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194671</v>
+        <v>125195512</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,43 +804,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596069</v>
+        <v>596000</v>
       </c>
       <c r="R3" t="n">
-        <v>6925880</v>
+        <v>6925950</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall.</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125194517</v>
+        <v>125192466</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,31 +921,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -958,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596060</v>
+        <v>596169</v>
       </c>
       <c r="R4" t="n">
-        <v>6925896</v>
+        <v>6925853</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,7 +998,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>10x</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125193041</v>
+        <v>125191762</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,43 +1042,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>595982</v>
+        <v>596138</v>
       </c>
       <c r="R5" t="n">
-        <v>6925883</v>
+        <v>6925797</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,12 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Väldigt många.</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,22 +1135,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125195720</v>
+        <v>125192424</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,30 +1159,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>90</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1196,10 +1192,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596021</v>
+        <v>596087</v>
       </c>
       <c r="R6" t="n">
-        <v>6925959</v>
+        <v>6925836</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1241,7 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125192314</v>
+        <v>125193908</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>105117</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1280,43 +1281,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596087</v>
+        <v>596085</v>
       </c>
       <c r="R7" t="n">
-        <v>6925836</v>
+        <v>6925872</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,12 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1378,22 +1369,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125192466</v>
+        <v>125192972</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,30 +1393,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1434,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596169</v>
+        <v>596152</v>
       </c>
       <c r="R8" t="n">
-        <v>6925853</v>
+        <v>6925878</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,12 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125191639</v>
+        <v>125194492</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,47 +1515,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596138</v>
+        <v>596063</v>
       </c>
       <c r="R9" t="n">
-        <v>6925797</v>
+        <v>6925899</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1595,7 +1582,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1605,12 +1592,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Myllgrop av tjäder + fjäder</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,22 +1607,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125192037</v>
+        <v>125194517</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1653,34 +1635,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596137</v>
+        <v>596060</v>
       </c>
       <c r="R10" t="n">
-        <v>6925817</v>
+        <v>6925896</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1722,7 +1709,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1737,22 +1724,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125196036</v>
+        <v>125194410</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1761,43 +1748,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596020</v>
+        <v>596069</v>
       </c>
       <c r="R11" t="n">
-        <v>6925933</v>
+        <v>6925880</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1829,7 +1815,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1839,7 +1825,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1866,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125195512</v>
+        <v>125194045</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1878,43 +1864,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596000</v>
+        <v>596078</v>
       </c>
       <c r="R12" t="n">
-        <v>6925950</v>
+        <v>6925853</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1946,7 +1931,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1956,7 +1941,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Kan finnas mer under löven</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125193908</v>
+        <v>125193041</v>
       </c>
       <c r="B13" t="n">
-        <v>105117</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1995,38 +1985,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596085</v>
+        <v>595982</v>
       </c>
       <c r="R13" t="n">
-        <v>6925872</v>
+        <v>6925883</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2058,7 +2053,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2068,7 +2063,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Väldigt många.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,19 +2083,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125194045</v>
+        <v>125195720</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2130,19 +2130,19 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596078</v>
+        <v>596021</v>
       </c>
       <c r="R14" t="n">
-        <v>6925853</v>
+        <v>6925959</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2184,12 +2184,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Kan finnas mer under löven</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2204,22 +2199,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125192972</v>
+        <v>125195800</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2228,43 +2223,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596152</v>
+        <v>596030</v>
       </c>
       <c r="R15" t="n">
-        <v>6925878</v>
+        <v>6925941</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2296,7 +2290,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2306,12 +2300,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2326,22 +2315,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125194278</v>
+        <v>125196940</v>
       </c>
       <c r="B16" t="n">
-        <v>96979</v>
+        <v>57666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2350,38 +2339,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596069</v>
+        <v>596026</v>
       </c>
       <c r="R16" t="n">
-        <v>6925880</v>
+        <v>6925885</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2413,7 +2407,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2423,7 +2417,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2438,22 +2432,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125192021</v>
+        <v>125192112</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>43834</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2462,43 +2456,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>101735</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596137</v>
+        <v>596164</v>
       </c>
       <c r="R17" t="n">
-        <v>6925817</v>
+        <v>6925821</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2530,7 +2519,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2540,12 +2529,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
+          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2560,22 +2549,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125192112</v>
+        <v>125192037</v>
       </c>
       <c r="B18" t="n">
-        <v>43834</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2584,38 +2573,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101735</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596164</v>
+        <v>596137</v>
       </c>
       <c r="R18" t="n">
-        <v>6925821</v>
+        <v>6925817</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2647,7 +2636,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2657,12 +2646,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2677,19 +2661,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125194304</v>
+        <v>125191997</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2730,14 +2714,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596074</v>
+        <v>596164</v>
       </c>
       <c r="R19" t="n">
-        <v>6925862</v>
+        <v>6925821</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2769,7 +2753,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2779,12 +2763,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2799,22 +2783,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125192270</v>
+        <v>125193970</v>
       </c>
       <c r="B20" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2827,34 +2811,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596164</v>
+        <v>596053</v>
       </c>
       <c r="R20" t="n">
-        <v>6925821</v>
+        <v>6925860</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2886,7 +2875,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2896,7 +2885,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2911,22 +2905,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125195800</v>
+        <v>125194278</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2935,42 +2929,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596030</v>
+        <v>596069</v>
       </c>
       <c r="R21" t="n">
-        <v>6925941</v>
+        <v>6925880</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3002,7 +2992,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3012,7 +3002,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3027,19 +3017,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125193970</v>
+        <v>125194304</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -3084,10 +3074,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596053</v>
+        <v>596074</v>
       </c>
       <c r="R22" t="n">
-        <v>6925860</v>
+        <v>6925862</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3119,7 +3109,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3129,7 +3119,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3161,10 +3151,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125196940</v>
+        <v>125193494</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3173,43 +3163,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596026</v>
+        <v>596117</v>
       </c>
       <c r="R23" t="n">
-        <v>6925885</v>
+        <v>6925846</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3241,7 +3230,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3251,7 +3240,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>* kan finnas mer under alla löv</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3266,19 +3260,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125191997</v>
+        <v>125193611</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3319,14 +3313,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596164</v>
+        <v>596006</v>
       </c>
       <c r="R24" t="n">
-        <v>6925821</v>
+        <v>6925913</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3358,7 +3352,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3368,12 +3362,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3388,22 +3382,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125194410</v>
+        <v>125191651</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3412,42 +3406,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>150</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>596069</v>
+        <v>596135</v>
       </c>
       <c r="R25" t="n">
-        <v>6925880</v>
+        <v>6925799</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3479,7 +3474,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3489,7 +3484,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3504,22 +3504,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125193331</v>
+        <v>125196036</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3528,43 +3528,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595959</v>
+        <v>596020</v>
       </c>
       <c r="R26" t="n">
-        <v>6925918</v>
+        <v>6925933</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3606,12 +3606,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3626,22 +3621,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125194219</v>
+        <v>125192270</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3650,42 +3645,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>596068</v>
+        <v>596164</v>
       </c>
       <c r="R27" t="n">
-        <v>6925867</v>
+        <v>6925821</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3717,7 +3708,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3727,7 +3718,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3754,10 +3745,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125195016</v>
+        <v>125192021</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3770,16 +3761,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3795,14 +3786,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596057</v>
+        <v>596137</v>
       </c>
       <c r="R28" t="n">
-        <v>6925928</v>
+        <v>6925817</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3834,7 +3825,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3844,7 +3835,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3859,22 +3855,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125191651</v>
+        <v>125194116</v>
       </c>
       <c r="B29" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3883,31 +3879,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3916,10 +3911,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596135</v>
+        <v>596053</v>
       </c>
       <c r="R29" t="n">
-        <v>6925799</v>
+        <v>6925860</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3951,7 +3946,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3961,12 +3956,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3993,10 +3983,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125194116</v>
+        <v>125194671</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4005,42 +3995,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596053</v>
+        <v>596069</v>
       </c>
       <c r="R30" t="n">
-        <v>6925860</v>
+        <v>6925880</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4072,7 +4063,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4082,7 +4073,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4097,19 +4093,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125193611</v>
+        <v>125193331</v>
       </c>
       <c r="B31" t="n">
         <v>57513</v>
@@ -4154,10 +4150,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596006</v>
+        <v>595959</v>
       </c>
       <c r="R31" t="n">
-        <v>6925913</v>
+        <v>6925918</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4189,7 +4185,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4199,7 +4195,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
@@ -4231,7 +4227,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125193494</v>
+        <v>125194219</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -4266,7 +4262,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4275,10 +4271,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596117</v>
+        <v>596068</v>
       </c>
       <c r="R32" t="n">
-        <v>6925846</v>
+        <v>6925867</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4310,7 +4306,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4320,12 +4316,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>* kan finnas mer under alla löv</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125195016</v>
+        <v>125193494</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596057</v>
+        <v>596117</v>
       </c>
       <c r="R2" t="n">
-        <v>6925928</v>
+        <v>6925846</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +764,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>* kan finnas mer under alla löv</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125195512</v>
+        <v>125192021</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,43 +808,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596000</v>
+        <v>596137</v>
       </c>
       <c r="R3" t="n">
-        <v>6925950</v>
+        <v>6925817</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,22 +906,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125192466</v>
+        <v>125193611</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,42 +930,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596169</v>
+        <v>596006</v>
       </c>
       <c r="R4" t="n">
-        <v>6925853</v>
+        <v>6925913</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,12 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,22 +1028,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125191762</v>
+        <v>125196940</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,43 +1052,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596138</v>
+        <v>596026</v>
       </c>
       <c r="R5" t="n">
-        <v>6925797</v>
+        <v>6925885</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,22 +1145,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125192424</v>
+        <v>125193908</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>105117</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,43 +1169,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596087</v>
+        <v>596085</v>
       </c>
       <c r="R6" t="n">
-        <v>6925836</v>
+        <v>6925872</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,22 +1257,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125193908</v>
+        <v>125192270</v>
       </c>
       <c r="B7" t="n">
-        <v>105117</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,25 +1281,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1309,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596085</v>
+        <v>596164</v>
       </c>
       <c r="R7" t="n">
-        <v>6925872</v>
+        <v>6925821</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125192972</v>
+        <v>125191762</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,31 +1393,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596152</v>
+        <v>596138</v>
       </c>
       <c r="R8" t="n">
-        <v>6925878</v>
+        <v>6925797</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,12 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125194492</v>
+        <v>125193331</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1515,30 +1510,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1547,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596063</v>
+        <v>595959</v>
       </c>
       <c r="R9" t="n">
-        <v>6925899</v>
+        <v>6925918</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1582,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1592,7 +1588,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1619,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125194517</v>
+        <v>125194045</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,31 +1632,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596060</v>
+        <v>596078</v>
       </c>
       <c r="R10" t="n">
-        <v>6925896</v>
+        <v>6925853</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,7 +1709,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Kan finnas mer under löven</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,7 +1741,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125194410</v>
+        <v>125194492</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1771,19 +1776,19 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596069</v>
+        <v>596063</v>
       </c>
       <c r="R11" t="n">
-        <v>6925880</v>
+        <v>6925899</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1825,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,19 +1845,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125194045</v>
+        <v>125192466</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1887,7 +1892,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1896,7 +1901,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596078</v>
+        <v>596169</v>
       </c>
       <c r="R12" t="n">
         <v>6925853</v>
@@ -1931,7 +1936,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1941,12 +1946,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Kan finnas mer under löven</t>
+          <t>10x</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,7 +1978,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125193041</v>
+        <v>125193970</v>
       </c>
       <c r="B13" t="n">
         <v>57513</v>
@@ -2018,10 +2023,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595982</v>
+        <v>596053</v>
       </c>
       <c r="R13" t="n">
-        <v>6925883</v>
+        <v>6925860</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,7 +2058,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2063,12 +2068,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Väldigt många.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,10 +2100,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125195720</v>
+        <v>125195512</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2107,42 +2112,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>90</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596021</v>
+        <v>596000</v>
       </c>
       <c r="R14" t="n">
-        <v>6925959</v>
+        <v>6925950</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2174,7 +2180,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2184,7 +2190,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2199,22 +2205,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125195800</v>
+        <v>125194304</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2223,30 +2229,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2255,10 +2262,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596030</v>
+        <v>596074</v>
       </c>
       <c r="R15" t="n">
-        <v>6925941</v>
+        <v>6925862</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2290,7 +2297,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2300,7 +2307,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2327,10 +2339,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125196940</v>
+        <v>125193041</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2343,27 +2355,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2372,10 +2384,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596026</v>
+        <v>595982</v>
       </c>
       <c r="R16" t="n">
-        <v>6925885</v>
+        <v>6925883</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2407,7 +2419,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2417,7 +2429,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Väldigt många.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2561,10 +2578,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125192037</v>
+        <v>125194278</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>96979</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2573,38 +2590,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596137</v>
+        <v>596069</v>
       </c>
       <c r="R18" t="n">
-        <v>6925817</v>
+        <v>6925880</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2636,7 +2653,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2646,7 +2663,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2661,19 +2678,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125191997</v>
+        <v>125192972</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2718,10 +2735,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596164</v>
+        <v>596152</v>
       </c>
       <c r="R19" t="n">
-        <v>6925821</v>
+        <v>6925878</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2753,7 +2770,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2763,12 +2780,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
+          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2795,7 +2812,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125193970</v>
+        <v>125191651</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2840,10 +2857,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596053</v>
+        <v>596135</v>
       </c>
       <c r="R20" t="n">
-        <v>6925860</v>
+        <v>6925799</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2875,7 +2892,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2885,7 +2902,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2917,10 +2934,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125194278</v>
+        <v>125196036</v>
       </c>
       <c r="B21" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2933,34 +2950,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596069</v>
+        <v>596020</v>
       </c>
       <c r="R21" t="n">
-        <v>6925880</v>
+        <v>6925933</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2992,7 +3014,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3002,7 +3024,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3029,10 +3051,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125194304</v>
+        <v>125195720</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3041,31 +3063,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>90</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3074,10 +3095,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596074</v>
+        <v>596021</v>
       </c>
       <c r="R22" t="n">
-        <v>6925862</v>
+        <v>6925959</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3109,7 +3130,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3119,12 +3140,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3151,10 +3167,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125193494</v>
+        <v>125192314</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3163,42 +3179,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>9</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596117</v>
+        <v>596087</v>
       </c>
       <c r="R23" t="n">
-        <v>6925846</v>
+        <v>6925836</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3230,7 +3247,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3240,12 +3257,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>* kan finnas mer under alla löv</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3260,19 +3277,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125193611</v>
+        <v>125194671</v>
       </c>
       <c r="B24" t="n">
         <v>57513</v>
@@ -3313,14 +3330,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596006</v>
+        <v>596069</v>
       </c>
       <c r="R24" t="n">
-        <v>6925913</v>
+        <v>6925880</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3352,7 +3369,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3362,12 +3379,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3382,22 +3399,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125191651</v>
+        <v>125195016</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3410,16 +3427,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3435,14 +3452,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>596135</v>
+        <v>596057</v>
       </c>
       <c r="R25" t="n">
-        <v>6925799</v>
+        <v>6925928</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3474,7 +3491,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3484,12 +3501,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3504,22 +3516,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125196036</v>
+        <v>125192037</v>
       </c>
       <c r="B26" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3528,43 +3540,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596020</v>
+        <v>596137</v>
       </c>
       <c r="R26" t="n">
-        <v>6925933</v>
+        <v>6925817</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3596,7 +3603,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3606,7 +3613,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3621,22 +3628,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125192270</v>
+        <v>125194410</v>
       </c>
       <c r="B27" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3645,38 +3652,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>596164</v>
+        <v>596069</v>
       </c>
       <c r="R27" t="n">
-        <v>6925821</v>
+        <v>6925880</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3708,7 +3719,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3718,7 +3729,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3745,7 +3756,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125192021</v>
+        <v>125191997</v>
       </c>
       <c r="B28" t="n">
         <v>57513</v>
@@ -3786,14 +3797,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596137</v>
+        <v>596164</v>
       </c>
       <c r="R28" t="n">
-        <v>6925817</v>
+        <v>6925821</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3825,7 +3836,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3835,12 +3846,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
+          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3855,22 +3866,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125194116</v>
+        <v>125194517</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3879,42 +3890,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596053</v>
+        <v>596060</v>
       </c>
       <c r="R29" t="n">
-        <v>6925860</v>
+        <v>6925896</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3946,7 +3958,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3956,7 +3968,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3971,22 +3983,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125194671</v>
+        <v>125194219</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3995,31 +4007,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4028,10 +4039,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596069</v>
+        <v>596068</v>
       </c>
       <c r="R30" t="n">
-        <v>6925880</v>
+        <v>6925867</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4063,7 +4074,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4073,12 +4084,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall.</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4105,10 +4111,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125193331</v>
+        <v>125195800</v>
       </c>
       <c r="B31" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4117,31 +4123,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4150,10 +4155,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>595959</v>
+        <v>596030</v>
       </c>
       <c r="R31" t="n">
-        <v>6925918</v>
+        <v>6925941</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4185,7 +4190,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4195,12 +4200,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4227,7 +4227,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125194219</v>
+        <v>125194116</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -4262,19 +4262,19 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596068</v>
+        <v>596053</v>
       </c>
       <c r="R32" t="n">
-        <v>6925867</v>
+        <v>6925860</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4331,12 +4331,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125192021</v>
+        <v>125195512</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,43 +808,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596137</v>
+        <v>596000</v>
       </c>
       <c r="R3" t="n">
-        <v>6925817</v>
+        <v>6925950</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,19 +901,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125193611</v>
+        <v>125194304</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -963,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596006</v>
+        <v>596074</v>
       </c>
       <c r="R4" t="n">
-        <v>6925913</v>
+        <v>6925862</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1003,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1040,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125196940</v>
+        <v>125192972</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,39 +1051,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596026</v>
+        <v>596152</v>
       </c>
       <c r="R5" t="n">
-        <v>6925885</v>
+        <v>6925878</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,22 +1145,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125193908</v>
+        <v>125192466</v>
       </c>
       <c r="B6" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,38 +1169,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596085</v>
+        <v>596169</v>
       </c>
       <c r="R6" t="n">
-        <v>6925872</v>
+        <v>6925853</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1246,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>10x</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125192270</v>
+        <v>125194278</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>96979</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,25 +1290,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1309,10 +1318,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596164</v>
+        <v>596069</v>
       </c>
       <c r="R7" t="n">
-        <v>6925821</v>
+        <v>6925880</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1363,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1390,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125191762</v>
+        <v>125195016</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,31 +1402,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1426,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596138</v>
+        <v>596057</v>
       </c>
       <c r="R8" t="n">
-        <v>6925797</v>
+        <v>6925928</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1620,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125194045</v>
+        <v>125192424</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,42 +1641,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596078</v>
+        <v>596087</v>
       </c>
       <c r="R10" t="n">
-        <v>6925853</v>
+        <v>6925836</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1699,7 +1709,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,12 +1719,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Kan finnas mer under löven</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,22 +1739,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125194492</v>
+        <v>125196940</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,30 +1763,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1785,10 +1796,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596063</v>
+        <v>596026</v>
       </c>
       <c r="R11" t="n">
-        <v>6925899</v>
+        <v>6925885</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,7 +1831,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1841,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,10 +1868,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125192466</v>
+        <v>125192037</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1869,42 +1880,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596169</v>
+        <v>596137</v>
       </c>
       <c r="R12" t="n">
-        <v>6925853</v>
+        <v>6925817</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1936,7 +1943,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1946,12 +1953,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>10x</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,22 +1968,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125193970</v>
+        <v>125191762</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1990,43 +1992,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596053</v>
+        <v>596138</v>
       </c>
       <c r="R13" t="n">
-        <v>6925860</v>
+        <v>6925797</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2058,7 +2060,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2068,12 +2070,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2088,22 +2085,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125195512</v>
+        <v>125194116</v>
       </c>
       <c r="B14" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2112,43 +2109,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596000</v>
+        <v>596053</v>
       </c>
       <c r="R14" t="n">
-        <v>6925950</v>
+        <v>6925860</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2180,7 +2176,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2190,7 +2186,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2205,22 +2201,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125194304</v>
+        <v>125194517</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2233,16 +2229,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2258,14 +2254,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596074</v>
+        <v>596060</v>
       </c>
       <c r="R15" t="n">
-        <v>6925862</v>
+        <v>6925896</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2297,7 +2293,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2307,12 +2303,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2327,19 +2318,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125193041</v>
+        <v>125193970</v>
       </c>
       <c r="B16" t="n">
         <v>57513</v>
@@ -2384,10 +2375,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595982</v>
+        <v>596053</v>
       </c>
       <c r="R16" t="n">
-        <v>6925883</v>
+        <v>6925860</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2419,7 +2410,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2429,12 +2420,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Väldigt många.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2461,10 +2452,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125192112</v>
+        <v>125192021</v>
       </c>
       <c r="B17" t="n">
-        <v>43834</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2473,38 +2464,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101735</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596164</v>
+        <v>596137</v>
       </c>
       <c r="R17" t="n">
-        <v>6925821</v>
+        <v>6925817</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2536,7 +2532,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2546,12 +2542,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
+          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2566,22 +2562,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125194278</v>
+        <v>125193611</v>
       </c>
       <c r="B18" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2590,38 +2586,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596069</v>
+        <v>596006</v>
       </c>
       <c r="R18" t="n">
-        <v>6925880</v>
+        <v>6925913</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2653,7 +2654,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2663,7 +2664,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2678,22 +2684,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125192972</v>
+        <v>125194410</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2702,31 +2708,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2735,10 +2740,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596152</v>
+        <v>596069</v>
       </c>
       <c r="R19" t="n">
-        <v>6925878</v>
+        <v>6925880</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2770,7 +2775,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2780,12 +2785,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2812,10 +2812,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125191651</v>
+        <v>125194492</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2824,31 +2824,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2857,10 +2856,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596135</v>
+        <v>596063</v>
       </c>
       <c r="R20" t="n">
-        <v>6925799</v>
+        <v>6925899</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2892,7 +2891,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2902,12 +2901,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3051,10 +3045,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125195720</v>
+        <v>125191997</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3063,42 +3057,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>90</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596021</v>
+        <v>596164</v>
       </c>
       <c r="R22" t="n">
-        <v>6925959</v>
+        <v>6925821</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3130,7 +3125,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3140,7 +3135,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3155,19 +3155,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125192314</v>
+        <v>125191651</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -3212,10 +3212,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596087</v>
+        <v>596135</v>
       </c>
       <c r="R23" t="n">
-        <v>6925836</v>
+        <v>6925799</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -3289,10 +3289,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125194671</v>
+        <v>125194045</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3301,31 +3301,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3334,10 +3333,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596069</v>
+        <v>596078</v>
       </c>
       <c r="R24" t="n">
-        <v>6925880</v>
+        <v>6925853</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3369,7 +3368,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3379,12 +3378,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall.</t>
+          <t>Kan finnas mer under löven</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3411,10 +3410,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125195016</v>
+        <v>125194671</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3427,16 +3426,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3456,10 +3455,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>596057</v>
+        <v>596069</v>
       </c>
       <c r="R25" t="n">
-        <v>6925928</v>
+        <v>6925880</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3491,7 +3490,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3501,7 +3500,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3528,10 +3532,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125192037</v>
+        <v>125193041</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3544,34 +3548,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596137</v>
+        <v>595982</v>
       </c>
       <c r="R26" t="n">
-        <v>6925817</v>
+        <v>6925883</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3603,7 +3612,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3613,7 +3622,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Väldigt många.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3640,10 +3654,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125194410</v>
+        <v>125192270</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3652,42 +3666,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>596069</v>
+        <v>596164</v>
       </c>
       <c r="R27" t="n">
-        <v>6925880</v>
+        <v>6925821</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3719,7 +3729,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3729,7 +3739,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3756,10 +3766,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125191997</v>
+        <v>125195800</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3768,43 +3778,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596164</v>
+        <v>596030</v>
       </c>
       <c r="R28" t="n">
-        <v>6925821</v>
+        <v>6925941</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3836,7 +3845,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3846,12 +3855,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3866,22 +3870,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125194517</v>
+        <v>125193908</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>105117</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3890,43 +3894,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596060</v>
+        <v>596085</v>
       </c>
       <c r="R29" t="n">
-        <v>6925896</v>
+        <v>6925872</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3958,7 +3957,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3968,7 +3967,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3995,10 +3994,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125194219</v>
+        <v>125192112</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>43834</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4007,42 +4006,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596068</v>
+        <v>596164</v>
       </c>
       <c r="R30" t="n">
-        <v>6925867</v>
+        <v>6925821</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4074,7 +4069,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4084,7 +4079,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4111,7 +4111,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125195800</v>
+        <v>125194219</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -4146,19 +4146,19 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596030</v>
+        <v>596068</v>
       </c>
       <c r="R31" t="n">
-        <v>6925941</v>
+        <v>6925867</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4190,7 +4190,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4215,19 +4215,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125194116</v>
+        <v>125195720</v>
       </c>
       <c r="B32" t="n">
         <v>98101</v>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4271,10 +4271,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596053</v>
+        <v>596021</v>
       </c>
       <c r="R32" t="n">
-        <v>6925860</v>
+        <v>6925959</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -1751,10 +1751,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125196940</v>
+        <v>125192037</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1767,39 +1767,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596026</v>
+        <v>596137</v>
       </c>
       <c r="R11" t="n">
-        <v>6925885</v>
+        <v>6925817</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1831,7 +1826,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1841,7 +1836,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1868,10 +1863,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125192037</v>
+        <v>125196940</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>57666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1884,34 +1879,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596137</v>
+        <v>596026</v>
       </c>
       <c r="R12" t="n">
-        <v>6925817</v>
+        <v>6925885</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -3289,10 +3289,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125194045</v>
+        <v>125194671</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3301,30 +3301,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3333,10 +3334,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596078</v>
+        <v>596069</v>
       </c>
       <c r="R24" t="n">
-        <v>6925853</v>
+        <v>6925880</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3368,7 +3369,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3378,12 +3379,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Kan finnas mer under löven</t>
+          <t>Ringhack av tretåig hackspett på Tall.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3410,7 +3411,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125194671</v>
+        <v>125193041</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3451,14 +3452,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>596069</v>
+        <v>595982</v>
       </c>
       <c r="R25" t="n">
-        <v>6925880</v>
+        <v>6925883</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3490,7 +3491,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3500,12 +3501,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall.</t>
+          <t>Ringhack på tall.  Väldigt många.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3520,22 +3521,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125193041</v>
+        <v>125194045</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3544,43 +3545,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>595982</v>
+        <v>596078</v>
       </c>
       <c r="R26" t="n">
-        <v>6925883</v>
+        <v>6925853</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Väldigt många.</t>
+          <t>Kan finnas mer under löven</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3642,12 +3642,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3766,10 +3766,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125195800</v>
+        <v>125193908</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3778,42 +3778,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596030</v>
+        <v>596085</v>
       </c>
       <c r="R28" t="n">
-        <v>6925941</v>
+        <v>6925872</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3845,7 +3841,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3855,7 +3851,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3870,22 +3866,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125193908</v>
+        <v>125195800</v>
       </c>
       <c r="B29" t="n">
-        <v>105117</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3894,38 +3890,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596085</v>
+        <v>596030</v>
       </c>
       <c r="R29" t="n">
-        <v>6925872</v>
+        <v>6925941</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3957,7 +3957,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3982,22 +3982,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125192112</v>
+        <v>125194219</v>
       </c>
       <c r="B30" t="n">
-        <v>43834</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4006,38 +4006,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101735</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596164</v>
+        <v>596068</v>
       </c>
       <c r="R30" t="n">
-        <v>6925821</v>
+        <v>6925867</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4069,7 +4073,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4079,12 +4083,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4111,10 +4110,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125194219</v>
+        <v>125192112</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>43834</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4123,42 +4122,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596068</v>
+        <v>596164</v>
       </c>
       <c r="R31" t="n">
-        <v>6925867</v>
+        <v>6925821</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4190,7 +4185,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4200,7 +4195,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125193494</v>
+        <v>125194410</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596117</v>
+        <v>596069</v>
       </c>
       <c r="R2" t="n">
-        <v>6925846</v>
+        <v>6925880</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>* kan finnas mer under alla löv</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125195512</v>
+        <v>125194278</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>96979</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,39 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596000</v>
+        <v>596069</v>
       </c>
       <c r="R3" t="n">
-        <v>6925950</v>
+        <v>6925880</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125194304</v>
+        <v>125194219</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,43 +915,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596074</v>
+        <v>596068</v>
       </c>
       <c r="R4" t="n">
-        <v>6925862</v>
+        <v>6925867</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,22 +1007,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125192972</v>
+        <v>125192270</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,39 +1035,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596152</v>
+        <v>596164</v>
       </c>
       <c r="R5" t="n">
-        <v>6925878</v>
+        <v>6925821</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1115,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1125,12 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,7 +1131,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125192466</v>
+        <v>125194045</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1192,7 +1166,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1201,7 +1175,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596169</v>
+        <v>596078</v>
       </c>
       <c r="R6" t="n">
         <v>6925853</v>
@@ -1236,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,12 +1220,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>Kan finnas mer under löven</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125194278</v>
+        <v>125192466</v>
       </c>
       <c r="B7" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,38 +1264,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596069</v>
+        <v>596169</v>
       </c>
       <c r="R7" t="n">
-        <v>6925880</v>
+        <v>6925853</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,7 +1341,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>10x</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125195016</v>
+        <v>125191762</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,31 +1385,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1435,10 +1418,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596057</v>
+        <v>596138</v>
       </c>
       <c r="R8" t="n">
-        <v>6925928</v>
+        <v>6925797</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,7 +1453,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1463,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,7 +1490,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125193331</v>
+        <v>125192972</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1548,14 +1531,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595959</v>
+        <v>596152</v>
       </c>
       <c r="R9" t="n">
-        <v>6925918</v>
+        <v>6925878</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,7 +1570,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,12 +1580,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,22 +1600,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125192424</v>
+        <v>125195512</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1641,43 +1624,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596087</v>
+        <v>596000</v>
       </c>
       <c r="R10" t="n">
-        <v>6925836</v>
+        <v>6925950</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1709,7 +1692,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1719,12 +1702,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,22 +1717,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125192037</v>
+        <v>125191651</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1767,34 +1745,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596137</v>
+        <v>596135</v>
       </c>
       <c r="R11" t="n">
-        <v>6925817</v>
+        <v>6925799</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1826,7 +1809,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1836,7 +1819,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1863,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125196940</v>
+        <v>125195720</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1875,31 +1863,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>90</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1908,10 +1895,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596026</v>
+        <v>596021</v>
       </c>
       <c r="R12" t="n">
-        <v>6925885</v>
+        <v>6925959</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1943,7 +1930,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1953,7 +1940,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1980,10 +1967,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125191762</v>
+        <v>125193494</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1992,31 +1979,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2025,10 +2011,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596138</v>
+        <v>596117</v>
       </c>
       <c r="R13" t="n">
-        <v>6925797</v>
+        <v>6925846</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2060,7 +2046,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2070,7 +2056,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>* kan finnas mer under alla löv</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2213,10 +2204,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125194517</v>
+        <v>125193331</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2229,16 +2220,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2254,14 +2245,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596060</v>
+        <v>595959</v>
       </c>
       <c r="R15" t="n">
-        <v>6925896</v>
+        <v>6925918</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2293,7 +2284,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2303,7 +2294,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2318,22 +2314,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125193970</v>
+        <v>125193908</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>105117</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2342,43 +2338,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596053</v>
+        <v>596085</v>
       </c>
       <c r="R16" t="n">
-        <v>6925860</v>
+        <v>6925872</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2410,7 +2401,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2420,12 +2411,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2440,22 +2426,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125192021</v>
+        <v>125194492</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2464,31 +2450,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2497,10 +2482,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596137</v>
+        <v>596063</v>
       </c>
       <c r="R17" t="n">
-        <v>6925817</v>
+        <v>6925899</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2532,7 +2517,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2542,12 +2527,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2574,7 +2554,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125193611</v>
+        <v>125193970</v>
       </c>
       <c r="B18" t="n">
         <v>57513</v>
@@ -2619,10 +2599,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596006</v>
+        <v>596053</v>
       </c>
       <c r="R18" t="n">
-        <v>6925913</v>
+        <v>6925860</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2654,7 +2634,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2664,7 +2644,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2696,10 +2676,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125194410</v>
+        <v>125194671</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2708,30 +2688,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>150</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2775,7 +2756,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2785,7 +2766,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2812,10 +2798,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125194492</v>
+        <v>125192037</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2824,42 +2810,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596063</v>
+        <v>596137</v>
       </c>
       <c r="R20" t="n">
-        <v>6925899</v>
+        <v>6925817</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2891,7 +2873,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2901,7 +2883,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2928,10 +2910,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125196036</v>
+        <v>125194517</v>
       </c>
       <c r="B21" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2940,43 +2922,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596020</v>
+        <v>596060</v>
       </c>
       <c r="R21" t="n">
-        <v>6925933</v>
+        <v>6925896</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3008,7 +2990,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3018,7 +3000,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3045,10 +3027,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125191997</v>
+        <v>125192112</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>43834</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3057,33 +3039,28 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>101735</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
@@ -3125,7 +3102,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3135,12 +3112,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
+          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3167,7 +3144,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125191651</v>
+        <v>125192021</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -3212,10 +3189,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596135</v>
+        <v>596137</v>
       </c>
       <c r="R23" t="n">
-        <v>6925799</v>
+        <v>6925817</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3247,7 +3224,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3257,12 +3234,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3289,10 +3266,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125194671</v>
+        <v>125196940</v>
       </c>
       <c r="B24" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3305,39 +3282,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596069</v>
+        <v>596026</v>
       </c>
       <c r="R24" t="n">
-        <v>6925880</v>
+        <v>6925885</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3369,7 +3346,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3379,12 +3356,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall.</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3399,19 +3371,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125193041</v>
+        <v>125192314</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3456,10 +3428,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>595982</v>
+        <v>596087</v>
       </c>
       <c r="R25" t="n">
-        <v>6925883</v>
+        <v>6925836</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3491,7 +3463,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3501,12 +3473,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Väldigt många.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3533,10 +3505,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125194045</v>
+        <v>125194304</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3545,42 +3517,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596078</v>
+        <v>596074</v>
       </c>
       <c r="R26" t="n">
-        <v>6925853</v>
+        <v>6925862</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3612,7 +3585,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3622,12 +3595,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Kan finnas mer under löven</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3642,22 +3615,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125192270</v>
+        <v>125191997</v>
       </c>
       <c r="B27" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3670,24 +3643,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
@@ -3729,7 +3707,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3739,7 +3717,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3766,10 +3749,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125193908</v>
+        <v>125193611</v>
       </c>
       <c r="B28" t="n">
-        <v>105117</v>
+        <v>57513</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3778,38 +3761,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596085</v>
+        <v>596006</v>
       </c>
       <c r="R28" t="n">
-        <v>6925872</v>
+        <v>6925913</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3841,7 +3829,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3851,7 +3839,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3866,22 +3859,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125195800</v>
+        <v>125195016</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3890,42 +3883,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596030</v>
+        <v>596057</v>
       </c>
       <c r="R29" t="n">
-        <v>6925941</v>
+        <v>6925928</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3957,7 +3951,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3967,7 +3961,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3982,22 +3976,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125194219</v>
+        <v>125196036</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4006,42 +4000,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596068</v>
+        <v>596020</v>
       </c>
       <c r="R30" t="n">
-        <v>6925867</v>
+        <v>6925933</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4073,7 +4068,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4083,7 +4078,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4110,10 +4105,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125192112</v>
+        <v>125195800</v>
       </c>
       <c r="B31" t="n">
-        <v>43834</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4122,38 +4117,42 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>101735</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596164</v>
+        <v>596030</v>
       </c>
       <c r="R31" t="n">
-        <v>6925821</v>
+        <v>6925941</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4185,7 +4184,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4195,12 +4194,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4215,22 +4209,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125195720</v>
+        <v>125193041</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4239,30 +4233,31 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>90</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4271,10 +4266,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596021</v>
+        <v>595982</v>
       </c>
       <c r="R32" t="n">
-        <v>6925959</v>
+        <v>6925883</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4306,7 +4301,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4316,7 +4311,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Väldigt många.</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -2204,10 +2204,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125193331</v>
+        <v>125193908</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>105117</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2216,43 +2216,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595959</v>
+        <v>596085</v>
       </c>
       <c r="R15" t="n">
-        <v>6925918</v>
+        <v>6925872</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2284,7 +2279,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2294,12 +2289,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2314,22 +2304,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125193908</v>
+        <v>125193331</v>
       </c>
       <c r="B16" t="n">
-        <v>105117</v>
+        <v>57513</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2338,38 +2328,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596085</v>
+        <v>595959</v>
       </c>
       <c r="R16" t="n">
-        <v>6925872</v>
+        <v>6925918</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2401,7 +2396,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2411,7 +2406,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2426,12 +2426,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2554,10 +2554,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125193970</v>
+        <v>125192037</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2570,39 +2570,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596053</v>
+        <v>596137</v>
       </c>
       <c r="R18" t="n">
-        <v>6925860</v>
+        <v>6925817</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2634,7 +2629,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2644,12 +2639,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2676,7 +2666,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125194671</v>
+        <v>125193970</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2717,14 +2707,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596069</v>
+        <v>596053</v>
       </c>
       <c r="R19" t="n">
-        <v>6925880</v>
+        <v>6925860</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2756,7 +2746,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2766,12 +2756,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2786,22 +2776,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125192037</v>
+        <v>125194671</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2814,34 +2804,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596137</v>
+        <v>596069</v>
       </c>
       <c r="R20" t="n">
-        <v>6925817</v>
+        <v>6925880</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2873,7 +2868,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2883,7 +2878,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2898,12 +2898,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125194410</v>
+        <v>125196940</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>150</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596069</v>
+        <v>596026</v>
       </c>
       <c r="R2" t="n">
-        <v>6925880</v>
+        <v>6925885</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194278</v>
+        <v>125195800</v>
       </c>
       <c r="B3" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +804,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596069</v>
+        <v>596030</v>
       </c>
       <c r="R3" t="n">
-        <v>6925880</v>
+        <v>6925941</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,22 +896,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125194219</v>
+        <v>125193908</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>105117</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,42 +920,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596068</v>
+        <v>596085</v>
       </c>
       <c r="R4" t="n">
-        <v>6925867</v>
+        <v>6925872</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1131,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125194045</v>
+        <v>125193970</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,42 +1144,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596078</v>
+        <v>596053</v>
       </c>
       <c r="R6" t="n">
-        <v>6925853</v>
+        <v>6925860</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,12 +1222,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Kan finnas mer under löven</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,22 +1242,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125192466</v>
+        <v>125195512</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,42 +1266,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596169</v>
+        <v>596000</v>
       </c>
       <c r="R7" t="n">
-        <v>6925853</v>
+        <v>6925950</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,12 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>10x</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125191762</v>
+        <v>125193331</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,43 +1383,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596138</v>
+        <v>595959</v>
       </c>
       <c r="R8" t="n">
-        <v>6925797</v>
+        <v>6925918</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1453,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1463,7 +1461,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,22 +1481,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125192972</v>
+        <v>125195016</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,16 +1509,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1535,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596152</v>
+        <v>596057</v>
       </c>
       <c r="R9" t="n">
-        <v>6925878</v>
+        <v>6925928</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,12 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125195512</v>
+        <v>125193041</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1624,43 +1622,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596000</v>
+        <v>595982</v>
       </c>
       <c r="R10" t="n">
-        <v>6925950</v>
+        <v>6925883</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1702,7 +1700,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Väldigt många.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,22 +1720,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125191651</v>
+        <v>125194517</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1745,16 +1748,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1770,14 +1773,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596135</v>
+        <v>596060</v>
       </c>
       <c r="R11" t="n">
-        <v>6925799</v>
+        <v>6925896</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,7 +1812,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1819,12 +1822,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,22 +1837,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125195720</v>
+        <v>125192314</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,30 +1861,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>90</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1895,10 +1894,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596021</v>
+        <v>596087</v>
       </c>
       <c r="R12" t="n">
-        <v>6925959</v>
+        <v>6925836</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,7 +1929,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1940,7 +1939,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1967,10 +1971,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125193494</v>
+        <v>125192112</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>43834</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1979,42 +1983,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596117</v>
+        <v>596164</v>
       </c>
       <c r="R13" t="n">
-        <v>6925846</v>
+        <v>6925821</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2056,12 +2056,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>* kan finnas mer under alla löv</t>
+          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2088,10 +2088,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125194116</v>
+        <v>125192972</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2100,42 +2100,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596053</v>
+        <v>596152</v>
       </c>
       <c r="R14" t="n">
-        <v>6925860</v>
+        <v>6925878</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2167,7 +2168,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2177,7 +2178,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,22 +2198,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125193908</v>
+        <v>125191639</v>
       </c>
       <c r="B15" t="n">
-        <v>105117</v>
+        <v>56722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,34 +2226,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596085</v>
+        <v>596138</v>
       </c>
       <c r="R15" t="n">
-        <v>6925872</v>
+        <v>6925797</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2279,7 +2294,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2289,7 +2304,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Myllgrop av tjäder + fjäder</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2316,10 +2336,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125193331</v>
+        <v>125193494</v>
       </c>
       <c r="B16" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,43 +2348,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>595959</v>
+        <v>596117</v>
       </c>
       <c r="R16" t="n">
-        <v>6925918</v>
+        <v>6925846</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2396,7 +2415,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2406,12 +2425,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>* kan finnas mer under alla löv</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2426,19 +2445,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125194492</v>
+        <v>125194116</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2473,7 +2492,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2482,10 +2501,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596063</v>
+        <v>596053</v>
       </c>
       <c r="R17" t="n">
-        <v>6925899</v>
+        <v>6925860</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2517,7 +2536,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2527,7 +2546,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2666,10 +2685,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125193970</v>
+        <v>125196036</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2678,43 +2697,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596053</v>
+        <v>596020</v>
       </c>
       <c r="R19" t="n">
-        <v>6925860</v>
+        <v>6925933</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2746,7 +2765,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2756,12 +2775,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,19 +2790,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125194671</v>
+        <v>125194304</v>
       </c>
       <c r="B20" t="n">
         <v>57513</v>
@@ -2829,14 +2843,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596069</v>
+        <v>596074</v>
       </c>
       <c r="R20" t="n">
-        <v>6925880</v>
+        <v>6925862</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2868,7 +2882,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2878,12 +2892,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2898,22 +2912,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125194517</v>
+        <v>125194410</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2922,31 +2936,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2955,10 +2968,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596060</v>
+        <v>596069</v>
       </c>
       <c r="R21" t="n">
-        <v>6925896</v>
+        <v>6925880</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2990,7 +3003,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3000,7 +3013,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3027,10 +3040,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125192112</v>
+        <v>125191997</v>
       </c>
       <c r="B22" t="n">
-        <v>43834</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3039,28 +3052,33 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>101735</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
@@ -3102,7 +3120,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3112,12 +3130,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
+          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3144,10 +3162,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125192021</v>
+        <v>125194278</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3156,43 +3174,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596137</v>
+        <v>596069</v>
       </c>
       <c r="R23" t="n">
-        <v>6925817</v>
+        <v>6925880</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3224,7 +3237,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3234,12 +3247,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3254,22 +3262,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125196940</v>
+        <v>125192466</v>
       </c>
       <c r="B24" t="n">
-        <v>57666</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3278,43 +3286,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596026</v>
+        <v>596169</v>
       </c>
       <c r="R24" t="n">
-        <v>6925885</v>
+        <v>6925853</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3346,7 +3353,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3356,7 +3363,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>10x</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3371,19 +3383,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125192314</v>
+        <v>125193611</v>
       </c>
       <c r="B25" t="n">
         <v>57513</v>
@@ -3428,10 +3440,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>596087</v>
+        <v>596006</v>
       </c>
       <c r="R25" t="n">
-        <v>6925836</v>
+        <v>6925913</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3463,7 +3475,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3473,7 +3485,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -3505,7 +3517,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125194304</v>
+        <v>125194671</v>
       </c>
       <c r="B26" t="n">
         <v>57513</v>
@@ -3546,14 +3558,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596074</v>
+        <v>596069</v>
       </c>
       <c r="R26" t="n">
-        <v>6925862</v>
+        <v>6925880</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3585,7 +3597,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3595,12 +3607,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3615,19 +3627,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125191997</v>
+        <v>125192021</v>
       </c>
       <c r="B27" t="n">
         <v>57513</v>
@@ -3668,14 +3680,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>596164</v>
+        <v>596137</v>
       </c>
       <c r="R27" t="n">
-        <v>6925821</v>
+        <v>6925817</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3707,7 +3719,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3717,12 +3729,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
+          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3737,22 +3749,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125193611</v>
+        <v>125195720</v>
       </c>
       <c r="B28" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3761,31 +3773,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>90</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3794,10 +3805,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596006</v>
+        <v>596021</v>
       </c>
       <c r="R28" t="n">
-        <v>6925913</v>
+        <v>6925959</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3829,7 +3840,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3839,12 +3850,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3871,10 +3877,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125195016</v>
+        <v>125194045</v>
       </c>
       <c r="B29" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3883,31 +3889,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3916,10 +3921,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596057</v>
+        <v>596078</v>
       </c>
       <c r="R29" t="n">
-        <v>6925928</v>
+        <v>6925853</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3951,7 +3956,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3961,7 +3966,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Kan finnas mer under löven</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3988,10 +3998,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125196036</v>
+        <v>125191651</v>
       </c>
       <c r="B30" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4000,43 +4010,43 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596020</v>
+        <v>596135</v>
       </c>
       <c r="R30" t="n">
-        <v>6925933</v>
+        <v>6925799</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4068,7 +4078,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4078,7 +4088,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4093,19 +4108,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125195800</v>
+        <v>125194492</v>
       </c>
       <c r="B31" t="n">
         <v>98101</v>
@@ -4140,7 +4155,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4149,10 +4164,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596030</v>
+        <v>596063</v>
       </c>
       <c r="R31" t="n">
-        <v>6925941</v>
+        <v>6925899</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4184,7 +4199,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4194,7 +4209,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4221,10 +4236,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125193041</v>
+        <v>125194219</v>
       </c>
       <c r="B32" t="n">
-        <v>57513</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4233,43 +4248,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>595982</v>
+        <v>596068</v>
       </c>
       <c r="R32" t="n">
-        <v>6925883</v>
+        <v>6925867</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4301,7 +4315,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4311,12 +4325,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Väldigt många.</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4331,12 +4340,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125196940</v>
+        <v>125194219</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596026</v>
+        <v>596068</v>
       </c>
       <c r="R2" t="n">
-        <v>6925885</v>
+        <v>6925867</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +779,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125195800</v>
+        <v>125194671</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,42 +803,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596030</v>
+        <v>596069</v>
       </c>
       <c r="R3" t="n">
-        <v>6925941</v>
+        <v>6925880</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,22 +901,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125193908</v>
+        <v>125192270</v>
       </c>
       <c r="B4" t="n">
-        <v>105117</v>
+        <v>80028</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,25 +925,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596085</v>
+        <v>596164</v>
       </c>
       <c r="R4" t="n">
-        <v>6925872</v>
+        <v>6925821</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125192270</v>
+        <v>125191762</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>56836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,38 +1037,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596164</v>
+        <v>596138</v>
       </c>
       <c r="R5" t="n">
-        <v>6925821</v>
+        <v>6925797</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125193970</v>
+        <v>125193331</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596053</v>
+        <v>595959</v>
       </c>
       <c r="R6" t="n">
-        <v>6925860</v>
+        <v>6925918</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1254,10 +1264,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125195512</v>
+        <v>125193494</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,43 +1276,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596000</v>
+        <v>596117</v>
       </c>
       <c r="R7" t="n">
-        <v>6925950</v>
+        <v>6925846</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1353,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>* kan finnas mer under alla löv</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125193331</v>
+        <v>125192037</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>91166</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,39 +1401,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595959</v>
+        <v>596137</v>
       </c>
       <c r="R8" t="n">
-        <v>6925918</v>
+        <v>6925817</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,12 +1470,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125195016</v>
+        <v>125193041</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,16 +1513,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1534,14 +1538,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596057</v>
+        <v>595982</v>
       </c>
       <c r="R9" t="n">
-        <v>6925928</v>
+        <v>6925883</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1577,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1587,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Väldigt många.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,22 +1607,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125193041</v>
+        <v>125192112</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>43932</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,43 +1631,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>101735</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>595982</v>
+        <v>596164</v>
       </c>
       <c r="R10" t="n">
-        <v>6925883</v>
+        <v>6925821</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,7 +1694,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,12 +1704,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Väldigt många.</t>
+          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,22 +1724,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125194517</v>
+        <v>125195800</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>98269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,43 +1748,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596060</v>
+        <v>596030</v>
       </c>
       <c r="R11" t="n">
-        <v>6925896</v>
+        <v>6925941</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1812,7 +1815,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1822,7 +1825,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,22 +1840,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125192314</v>
+        <v>125195512</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>56836</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1861,43 +1864,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596087</v>
+        <v>596000</v>
       </c>
       <c r="R12" t="n">
-        <v>6925836</v>
+        <v>6925950</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1929,7 +1932,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1939,12 +1942,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1959,22 +1957,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125192112</v>
+        <v>125192021</v>
       </c>
       <c r="B13" t="n">
-        <v>43834</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,38 +1981,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101735</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596164</v>
+        <v>596137</v>
       </c>
       <c r="R13" t="n">
-        <v>6925821</v>
+        <v>6925817</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2046,7 +2049,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2056,12 +2059,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
+          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2076,22 +2079,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125192972</v>
+        <v>125191651</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2129,14 +2132,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596152</v>
+        <v>596135</v>
       </c>
       <c r="R14" t="n">
-        <v>6925878</v>
+        <v>6925799</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2168,7 +2171,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2178,12 +2181,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2198,22 +2201,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125191639</v>
+        <v>125193970</v>
       </c>
       <c r="B15" t="n">
-        <v>56722</v>
+        <v>57635</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2222,32 +2225,28 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -2255,14 +2254,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596138</v>
+        <v>596053</v>
       </c>
       <c r="R15" t="n">
-        <v>6925797</v>
+        <v>6925860</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2294,7 +2293,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2304,12 +2303,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Myllgrop av tjäder + fjäder</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2324,22 +2323,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125193494</v>
+        <v>125192424</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>57635</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2348,42 +2347,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>9</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596117</v>
+        <v>596087</v>
       </c>
       <c r="R16" t="n">
-        <v>6925846</v>
+        <v>6925836</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2415,7 +2415,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2425,12 +2425,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>* kan finnas mer under alla löv</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2445,22 +2445,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125194116</v>
+        <v>125196036</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>56836</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2469,42 +2469,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596053</v>
+        <v>596020</v>
       </c>
       <c r="R17" t="n">
-        <v>6925860</v>
+        <v>6925933</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2536,7 +2537,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2546,7 +2547,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2561,22 +2562,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125192037</v>
+        <v>125194410</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>98269</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2585,38 +2586,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596137</v>
+        <v>596069</v>
       </c>
       <c r="R18" t="n">
-        <v>6925817</v>
+        <v>6925880</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2648,7 +2653,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2658,7 +2663,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,22 +2678,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125196036</v>
+        <v>125194278</v>
       </c>
       <c r="B19" t="n">
-        <v>56722</v>
+        <v>97147</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2701,39 +2706,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596020</v>
+        <v>596069</v>
       </c>
       <c r="R19" t="n">
-        <v>6925933</v>
+        <v>6925880</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2802,10 +2802,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125194304</v>
+        <v>125192466</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>98269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2814,43 +2814,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596074</v>
+        <v>596169</v>
       </c>
       <c r="R20" t="n">
-        <v>6925862</v>
+        <v>6925853</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2882,7 +2881,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2892,12 +2891,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>10x</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2912,22 +2911,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125194410</v>
+        <v>125195016</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>57632</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2936,30 +2935,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>150</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596069</v>
+        <v>596057</v>
       </c>
       <c r="R21" t="n">
-        <v>6925880</v>
+        <v>6925928</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3040,10 +3040,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125191997</v>
+        <v>125193908</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>105293</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3052,43 +3052,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>221144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596164</v>
+        <v>596085</v>
       </c>
       <c r="R22" t="n">
-        <v>6925821</v>
+        <v>6925872</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3120,7 +3115,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3130,12 +3125,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3162,10 +3152,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125194278</v>
+        <v>125194116</v>
       </c>
       <c r="B23" t="n">
-        <v>96979</v>
+        <v>98269</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3174,38 +3164,42 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596069</v>
+        <v>596053</v>
       </c>
       <c r="R23" t="n">
-        <v>6925880</v>
+        <v>6925860</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3237,7 +3231,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3247,7 +3241,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3262,22 +3256,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125192466</v>
+        <v>125192972</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>57635</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3286,30 +3280,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3318,10 +3313,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596169</v>
+        <v>596152</v>
       </c>
       <c r="R24" t="n">
-        <v>6925853</v>
+        <v>6925878</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3353,7 +3348,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3363,12 +3358,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3395,10 +3390,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125193611</v>
+        <v>125194517</v>
       </c>
       <c r="B25" t="n">
-        <v>57513</v>
+        <v>57632</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3411,16 +3406,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3436,14 +3431,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>596006</v>
+        <v>596060</v>
       </c>
       <c r="R25" t="n">
-        <v>6925913</v>
+        <v>6925896</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3475,7 +3470,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3485,12 +3480,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3505,22 +3495,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125194671</v>
+        <v>125194492</v>
       </c>
       <c r="B26" t="n">
-        <v>57513</v>
+        <v>98269</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3529,43 +3519,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596069</v>
+        <v>596063</v>
       </c>
       <c r="R26" t="n">
-        <v>6925880</v>
+        <v>6925899</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3597,7 +3586,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3607,12 +3596,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall.</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3627,22 +3611,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125192021</v>
+        <v>125195720</v>
       </c>
       <c r="B27" t="n">
-        <v>57513</v>
+        <v>98269</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3651,31 +3635,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>90</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3684,10 +3667,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>596137</v>
+        <v>596021</v>
       </c>
       <c r="R27" t="n">
-        <v>6925817</v>
+        <v>6925959</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3719,7 +3702,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3729,12 +3712,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3761,10 +3739,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125195720</v>
+        <v>125194304</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>57635</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3773,30 +3751,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>90</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3805,10 +3784,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596021</v>
+        <v>596074</v>
       </c>
       <c r="R28" t="n">
-        <v>6925959</v>
+        <v>6925862</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3840,7 +3819,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3850,7 +3829,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3877,10 +3861,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125194045</v>
+        <v>125191997</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>57635</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3889,30 +3873,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3921,10 +3906,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596078</v>
+        <v>596164</v>
       </c>
       <c r="R29" t="n">
-        <v>6925853</v>
+        <v>6925821</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3956,7 +3941,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3966,12 +3951,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Kan finnas mer under löven</t>
+          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3998,10 +3983,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125191651</v>
+        <v>125193611</v>
       </c>
       <c r="B30" t="n">
-        <v>57513</v>
+        <v>57635</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4043,10 +4028,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596135</v>
+        <v>596006</v>
       </c>
       <c r="R30" t="n">
-        <v>6925799</v>
+        <v>6925913</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4078,7 +4063,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4088,7 +4073,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4120,10 +4105,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125194492</v>
+        <v>125196940</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>57793</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4132,30 +4117,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4164,10 +4150,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596063</v>
+        <v>596026</v>
       </c>
       <c r="R31" t="n">
-        <v>6925899</v>
+        <v>6925885</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4199,7 +4185,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4209,7 +4195,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4236,10 +4222,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125194219</v>
+        <v>125194045</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4271,7 +4257,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4280,10 +4266,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596068</v>
+        <v>596078</v>
       </c>
       <c r="R32" t="n">
-        <v>6925867</v>
+        <v>6925853</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4315,7 +4301,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4325,7 +4311,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Kan finnas mer under löven</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -1852,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125195512</v>
+        <v>125192021</v>
       </c>
       <c r="B12" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1864,43 +1864,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596000</v>
+        <v>596137</v>
       </c>
       <c r="R12" t="n">
-        <v>6925950</v>
+        <v>6925817</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1942,7 +1942,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,19 +1962,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125192021</v>
+        <v>125191651</v>
       </c>
       <c r="B13" t="n">
         <v>57635</v>
@@ -2014,10 +2019,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596137</v>
+        <v>596135</v>
       </c>
       <c r="R13" t="n">
-        <v>6925817</v>
+        <v>6925799</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2049,7 +2054,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2059,12 +2064,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,10 +2096,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125191651</v>
+        <v>125195512</v>
       </c>
       <c r="B14" t="n">
-        <v>57635</v>
+        <v>56836</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2103,43 +2108,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596135</v>
+        <v>596000</v>
       </c>
       <c r="R14" t="n">
-        <v>6925799</v>
+        <v>6925950</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2171,7 +2176,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2181,12 +2186,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2201,12 +2201,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -3152,10 +3152,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125194116</v>
+        <v>125192972</v>
       </c>
       <c r="B23" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3164,42 +3164,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596053</v>
+        <v>596152</v>
       </c>
       <c r="R23" t="n">
-        <v>6925860</v>
+        <v>6925878</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3231,7 +3232,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3241,7 +3242,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3256,22 +3262,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125192972</v>
+        <v>125194116</v>
       </c>
       <c r="B24" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3280,43 +3286,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596152</v>
+        <v>596053</v>
       </c>
       <c r="R24" t="n">
-        <v>6925878</v>
+        <v>6925860</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3348,7 +3353,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3358,12 +3363,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3378,12 +3378,12 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125194219</v>
+        <v>125192112</v>
       </c>
       <c r="B2" t="n">
-        <v>98269</v>
+        <v>43932</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>101735</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596068</v>
+        <v>596164</v>
       </c>
       <c r="R2" t="n">
-        <v>6925867</v>
+        <v>6925821</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194671</v>
+        <v>125191762</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
+        <v>56836</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,31 +804,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596069</v>
+        <v>596138</v>
       </c>
       <c r="R3" t="n">
-        <v>6925880</v>
+        <v>6925797</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall.</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125192270</v>
+        <v>125194492</v>
       </c>
       <c r="B4" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,38 +921,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596164</v>
+        <v>596063</v>
       </c>
       <c r="R4" t="n">
-        <v>6925821</v>
+        <v>6925899</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125191762</v>
+        <v>125194671</v>
       </c>
       <c r="B5" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596138</v>
+        <v>596069</v>
       </c>
       <c r="R5" t="n">
-        <v>6925797</v>
+        <v>6925880</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,7 +1147,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125193331</v>
+        <v>125191997</v>
       </c>
       <c r="B6" t="n">
         <v>57635</v>
@@ -1183,14 +1188,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>595959</v>
+        <v>596164</v>
       </c>
       <c r="R6" t="n">
-        <v>6925918</v>
+        <v>6925821</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1227,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,12 +1237,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,22 +1257,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125193494</v>
+        <v>125192021</v>
       </c>
       <c r="B7" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,42 +1281,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>9</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596117</v>
+        <v>596137</v>
       </c>
       <c r="R7" t="n">
-        <v>6925846</v>
+        <v>6925817</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,12 +1359,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>* kan finnas mer under alla löv</t>
+          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,22 +1379,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125192037</v>
+        <v>125196036</v>
       </c>
       <c r="B8" t="n">
-        <v>91166</v>
+        <v>56836</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,38 +1403,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596137</v>
+        <v>596020</v>
       </c>
       <c r="R8" t="n">
-        <v>6925817</v>
+        <v>6925933</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,7 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,22 +1496,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125193041</v>
+        <v>125192270</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
+        <v>80028</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1513,39 +1524,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>595982</v>
+        <v>596164</v>
       </c>
       <c r="R9" t="n">
-        <v>6925883</v>
+        <v>6925821</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1577,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1587,12 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.  Väldigt många.</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,22 +1608,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125192112</v>
+        <v>125193908</v>
       </c>
       <c r="B10" t="n">
-        <v>43932</v>
+        <v>105293</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,21 +1636,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101735</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1659,10 +1660,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596164</v>
+        <v>596085</v>
       </c>
       <c r="R10" t="n">
-        <v>6925821</v>
+        <v>6925872</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1694,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1704,12 +1705,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,7 +1732,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125195800</v>
+        <v>125194045</v>
       </c>
       <c r="B11" t="n">
         <v>98269</v>
@@ -1771,19 +1767,19 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596030</v>
+        <v>596078</v>
       </c>
       <c r="R11" t="n">
-        <v>6925941</v>
+        <v>6925853</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,7 +1811,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1825,7 +1821,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Kan finnas mer under löven</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,22 +1841,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125192021</v>
+        <v>125192037</v>
       </c>
       <c r="B12" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,29 +1869,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Öster-svarttjärn, Mpd</t>
@@ -1932,7 +1928,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1942,12 +1938,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1974,10 +1965,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125191651</v>
+        <v>125194517</v>
       </c>
       <c r="B13" t="n">
-        <v>57635</v>
+        <v>57632</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1990,16 +1981,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2015,14 +2006,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596135</v>
+        <v>596060</v>
       </c>
       <c r="R13" t="n">
-        <v>6925799</v>
+        <v>6925896</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2054,7 +2045,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2064,12 +2055,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2084,22 +2070,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125195512</v>
+        <v>125193970</v>
       </c>
       <c r="B14" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2108,43 +2094,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596000</v>
+        <v>596053</v>
       </c>
       <c r="R14" t="n">
-        <v>6925950</v>
+        <v>6925860</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2176,7 +2162,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2186,7 +2172,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2201,19 +2192,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125193970</v>
+        <v>125193041</v>
       </c>
       <c r="B15" t="n">
         <v>57635</v>
@@ -2258,10 +2249,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596053</v>
+        <v>595982</v>
       </c>
       <c r="R15" t="n">
-        <v>6925860</v>
+        <v>6925883</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2293,7 +2284,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2303,12 +2294,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall.  Väldigt många.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2335,7 +2326,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125192424</v>
+        <v>125191651</v>
       </c>
       <c r="B16" t="n">
         <v>57635</v>
@@ -2380,10 +2371,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596087</v>
+        <v>596135</v>
       </c>
       <c r="R16" t="n">
-        <v>6925836</v>
+        <v>6925799</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2415,7 +2406,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2425,7 +2416,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2457,10 +2448,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125196036</v>
+        <v>125194304</v>
       </c>
       <c r="B17" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2469,43 +2460,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596020</v>
+        <v>596074</v>
       </c>
       <c r="R17" t="n">
-        <v>6925933</v>
+        <v>6925862</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2537,7 +2528,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2547,7 +2538,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2562,22 +2558,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125194410</v>
+        <v>125194278</v>
       </c>
       <c r="B18" t="n">
-        <v>98269</v>
+        <v>97147</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2586,32 +2582,28 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
@@ -2653,7 +2645,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2663,7 +2655,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2690,10 +2682,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125194278</v>
+        <v>125192314</v>
       </c>
       <c r="B19" t="n">
-        <v>97147</v>
+        <v>57635</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2702,38 +2694,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596069</v>
+        <v>596087</v>
       </c>
       <c r="R19" t="n">
-        <v>6925880</v>
+        <v>6925836</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2765,7 +2762,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2775,7 +2772,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2790,22 +2792,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125192466</v>
+        <v>125193331</v>
       </c>
       <c r="B20" t="n">
-        <v>98269</v>
+        <v>57635</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2814,42 +2816,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596169</v>
+        <v>595959</v>
       </c>
       <c r="R20" t="n">
-        <v>6925853</v>
+        <v>6925918</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2881,7 +2884,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2891,12 +2894,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2911,22 +2914,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125195016</v>
+        <v>125193611</v>
       </c>
       <c r="B21" t="n">
-        <v>57632</v>
+        <v>57635</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2939,16 +2942,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2964,14 +2967,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596057</v>
+        <v>596006</v>
       </c>
       <c r="R21" t="n">
-        <v>6925928</v>
+        <v>6925913</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3003,7 +3006,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3013,7 +3016,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3028,22 +3036,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125193908</v>
+        <v>125194410</v>
       </c>
       <c r="B22" t="n">
-        <v>105293</v>
+        <v>98269</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3052,38 +3060,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596085</v>
+        <v>596069</v>
       </c>
       <c r="R22" t="n">
-        <v>6925872</v>
+        <v>6925880</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3115,7 +3127,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3125,7 +3137,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3152,10 +3164,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125192972</v>
+        <v>125194219</v>
       </c>
       <c r="B23" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3164,31 +3176,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3197,10 +3208,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596152</v>
+        <v>596068</v>
       </c>
       <c r="R23" t="n">
-        <v>6925878</v>
+        <v>6925867</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3232,7 +3243,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3242,12 +3253,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3274,10 +3280,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125194116</v>
+        <v>125196940</v>
       </c>
       <c r="B24" t="n">
-        <v>98269</v>
+        <v>57793</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3286,30 +3292,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3318,10 +3325,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596053</v>
+        <v>596026</v>
       </c>
       <c r="R24" t="n">
-        <v>6925860</v>
+        <v>6925885</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3353,7 +3360,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3363,7 +3370,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3390,10 +3397,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125194517</v>
+        <v>125194116</v>
       </c>
       <c r="B25" t="n">
-        <v>57632</v>
+        <v>98269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3402,43 +3409,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>596060</v>
+        <v>596053</v>
       </c>
       <c r="R25" t="n">
-        <v>6925896</v>
+        <v>6925860</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3470,7 +3476,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3480,7 +3486,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3495,19 +3501,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125194492</v>
+        <v>125193494</v>
       </c>
       <c r="B26" t="n">
         <v>98269</v>
@@ -3542,19 +3548,19 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596063</v>
+        <v>596117</v>
       </c>
       <c r="R26" t="n">
-        <v>6925899</v>
+        <v>6925846</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3586,7 +3592,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3596,7 +3602,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>* kan finnas mer under alla löv</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3611,22 +3622,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125195720</v>
+        <v>125195016</v>
       </c>
       <c r="B27" t="n">
-        <v>98269</v>
+        <v>57632</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3635,42 +3646,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>90</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>596021</v>
+        <v>596057</v>
       </c>
       <c r="R27" t="n">
-        <v>6925959</v>
+        <v>6925928</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3702,7 +3714,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3712,7 +3724,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3727,22 +3739,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125194304</v>
+        <v>125195720</v>
       </c>
       <c r="B28" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3751,31 +3763,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>90</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3784,10 +3795,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596074</v>
+        <v>596021</v>
       </c>
       <c r="R28" t="n">
-        <v>6925862</v>
+        <v>6925959</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3819,7 +3830,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3829,12 +3840,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3861,10 +3867,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125191997</v>
+        <v>125195512</v>
       </c>
       <c r="B29" t="n">
-        <v>57635</v>
+        <v>56836</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3873,43 +3879,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596164</v>
+        <v>596000</v>
       </c>
       <c r="R29" t="n">
-        <v>6925821</v>
+        <v>6925950</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3941,7 +3947,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3951,12 +3957,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:41</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3983,10 +3984,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125193611</v>
+        <v>125192466</v>
       </c>
       <c r="B30" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3995,43 +3996,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596006</v>
+        <v>596169</v>
       </c>
       <c r="R30" t="n">
-        <v>6925913</v>
+        <v>6925853</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>10x</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4093,22 +4093,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125196940</v>
+        <v>125192972</v>
       </c>
       <c r="B31" t="n">
-        <v>57793</v>
+        <v>57635</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4121,39 +4121,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596026</v>
+        <v>596152</v>
       </c>
       <c r="R31" t="n">
-        <v>6925885</v>
+        <v>6925878</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4195,7 +4195,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4210,19 +4215,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125194045</v>
+        <v>125195800</v>
       </c>
       <c r="B32" t="n">
         <v>98269</v>
@@ -4257,19 +4262,19 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>35</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596078</v>
+        <v>596030</v>
       </c>
       <c r="R32" t="n">
-        <v>6925853</v>
+        <v>6925941</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4301,7 +4306,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4311,12 +4316,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Kan finnas mer under löven</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4331,12 +4331,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125192021</v>
+        <v>125196036</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
+        <v>56836</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,43 +1281,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596137</v>
+        <v>596020</v>
       </c>
       <c r="R7" t="n">
-        <v>6925817</v>
+        <v>6925933</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,12 +1359,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1379,22 +1374,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125196036</v>
+        <v>125192021</v>
       </c>
       <c r="B8" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,43 +1398,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596020</v>
+        <v>596137</v>
       </c>
       <c r="R8" t="n">
-        <v>6925933</v>
+        <v>6925817</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1476,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,12 +1496,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125194410</v>
+        <v>125194219</v>
       </c>
       <c r="B22" t="n">
         <v>98269</v>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3092,10 +3092,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596069</v>
+        <v>596068</v>
       </c>
       <c r="R22" t="n">
-        <v>6925880</v>
+        <v>6925867</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3127,7 +3127,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3164,7 +3164,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125194219</v>
+        <v>125194410</v>
       </c>
       <c r="B23" t="n">
         <v>98269</v>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596068</v>
+        <v>596069</v>
       </c>
       <c r="R23" t="n">
-        <v>6925867</v>
+        <v>6925880</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -1269,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125196036</v>
+        <v>125192021</v>
       </c>
       <c r="B7" t="n">
-        <v>56836</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,43 +1281,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596020</v>
+        <v>596137</v>
       </c>
       <c r="R7" t="n">
-        <v>6925933</v>
+        <v>6925817</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1359,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,22 +1379,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125192021</v>
+        <v>125196036</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
+        <v>56836</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1398,43 +1403,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596137</v>
+        <v>596020</v>
       </c>
       <c r="R8" t="n">
-        <v>6925817</v>
+        <v>6925933</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,12 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,22 +1496,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125192270</v>
+        <v>125193908</v>
       </c>
       <c r="B9" t="n">
-        <v>80028</v>
+        <v>105293</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,25 +1520,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596164</v>
+        <v>596085</v>
       </c>
       <c r="R9" t="n">
-        <v>6925821</v>
+        <v>6925872</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125193908</v>
+        <v>125192270</v>
       </c>
       <c r="B10" t="n">
-        <v>105293</v>
+        <v>80028</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,25 +1632,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1660,10 +1660,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596085</v>
+        <v>596164</v>
       </c>
       <c r="R10" t="n">
-        <v>6925872</v>
+        <v>6925821</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125194045</v>
+        <v>125192037</v>
       </c>
       <c r="B11" t="n">
-        <v>98269</v>
+        <v>91166</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,42 +1744,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596078</v>
+        <v>596137</v>
       </c>
       <c r="R11" t="n">
-        <v>6925853</v>
+        <v>6925817</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1811,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1821,12 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Kan finnas mer under löven</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,22 +1832,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125192037</v>
+        <v>125194517</v>
       </c>
       <c r="B12" t="n">
-        <v>91166</v>
+        <v>57632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1869,34 +1860,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596137</v>
+        <v>596060</v>
       </c>
       <c r="R12" t="n">
-        <v>6925817</v>
+        <v>6925896</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1928,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1938,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1953,22 +1949,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125194517</v>
+        <v>125193970</v>
       </c>
       <c r="B13" t="n">
-        <v>57632</v>
+        <v>57635</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1981,16 +1977,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2006,14 +2002,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596060</v>
+        <v>596053</v>
       </c>
       <c r="R13" t="n">
-        <v>6925896</v>
+        <v>6925860</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2045,7 +2041,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2055,7 +2051,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2070,22 +2071,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125193970</v>
+        <v>125194045</v>
       </c>
       <c r="B14" t="n">
-        <v>57635</v>
+        <v>98269</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2094,43 +2095,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596053</v>
+        <v>596078</v>
       </c>
       <c r="R14" t="n">
-        <v>6925860</v>
+        <v>6925853</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Kan finnas mer under löven</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,12 +2192,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -675,50 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125192112</v>
+        <v>125192424</v>
       </c>
       <c r="B2" t="n">
-        <v>43932</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101735</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596164</v>
+        <v>596087</v>
       </c>
       <c r="R2" t="n">
-        <v>6925821</v>
+        <v>6925836</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,67 +780,61 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125191762</v>
+        <v>125194492</v>
       </c>
       <c r="B3" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596138</v>
+        <v>596063</v>
       </c>
       <c r="R3" t="n">
-        <v>6925797</v>
+        <v>6925899</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,27 +891,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125194492</v>
+        <v>125194116</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,7 +933,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -953,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596063</v>
+        <v>596053</v>
       </c>
       <c r="R4" t="n">
-        <v>6925899</v>
+        <v>6925860</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,15 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125194671</v>
+        <v>125193611</v>
       </c>
       <c r="B5" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,14 +1050,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596069</v>
+        <v>596006</v>
       </c>
       <c r="R5" t="n">
-        <v>6925880</v>
+        <v>6925913</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1099,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,27 +1119,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125191997</v>
+        <v>125192021</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1188,14 +1167,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596164</v>
+        <v>596137</v>
       </c>
       <c r="R6" t="n">
-        <v>6925821</v>
+        <v>6925817</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1237,12 +1216,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
+          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,27 +1236,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125192021</v>
+        <v>125193331</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1314,10 +1288,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596137</v>
+        <v>595959</v>
       </c>
       <c r="R7" t="n">
-        <v>6925817</v>
+        <v>6925918</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1349,7 +1323,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,12 +1333,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,55 +1365,49 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125196036</v>
+        <v>125195800</v>
       </c>
       <c r="B8" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596020</v>
+        <v>596030</v>
       </c>
       <c r="R8" t="n">
-        <v>6925933</v>
+        <v>6925941</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1449,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,62 +1464,61 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125193908</v>
+        <v>125192466</v>
       </c>
       <c r="B9" t="n">
-        <v>105293</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596085</v>
+        <v>596169</v>
       </c>
       <c r="R9" t="n">
-        <v>6925872</v>
+        <v>6925853</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1583,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1593,7 +1560,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>10x</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,50 +1592,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125192270</v>
+        <v>125191639</v>
       </c>
       <c r="B10" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596164</v>
+        <v>596138</v>
       </c>
       <c r="R10" t="n">
-        <v>6925821</v>
+        <v>6925797</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,7 +1681,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Myllgrop av tjäder + fjäder</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,15 +1713,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125192037</v>
+        <v>125196940</v>
       </c>
       <c r="B11" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1748,34 +1724,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596137</v>
+        <v>596026</v>
       </c>
       <c r="R11" t="n">
-        <v>6925817</v>
+        <v>6925885</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,7 +1788,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1798,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,55 +1825,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125194517</v>
+        <v>125193908</v>
       </c>
       <c r="B12" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596060</v>
+        <v>596085</v>
       </c>
       <c r="R12" t="n">
-        <v>6925896</v>
+        <v>6925872</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,55 +1932,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125193970</v>
+        <v>125192112</v>
       </c>
       <c r="B13" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43933</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>101735</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596053</v>
+        <v>596164</v>
       </c>
       <c r="R13" t="n">
-        <v>6925860</v>
+        <v>6925821</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2041,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2051,12 +2012,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,66 +2032,62 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125194045</v>
+        <v>125193041</v>
       </c>
       <c r="B14" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596078</v>
+        <v>595982</v>
       </c>
       <c r="R14" t="n">
-        <v>6925853</v>
+        <v>6925883</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2162,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2172,12 +2129,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Kan finnas mer under löven</t>
+          <t>Ringhack på tall.  Väldigt många.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2192,27 +2149,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125193041</v>
+        <v>125193970</v>
       </c>
       <c r="B15" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2249,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>595982</v>
+        <v>596053</v>
       </c>
       <c r="R15" t="n">
-        <v>6925883</v>
+        <v>6925860</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2284,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2294,12 +2246,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Väldigt många.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2326,15 +2278,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125191651</v>
+        <v>125194671</v>
       </c>
       <c r="B16" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2367,14 +2314,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596135</v>
+        <v>596069</v>
       </c>
       <c r="R16" t="n">
-        <v>6925799</v>
+        <v>6925880</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2406,7 +2353,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2416,12 +2363,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2436,27 +2383,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125194304</v>
+        <v>125191997</v>
       </c>
       <c r="B17" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2489,14 +2431,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596074</v>
+        <v>596164</v>
       </c>
       <c r="R17" t="n">
-        <v>6925862</v>
+        <v>6925821</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2528,7 +2470,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2538,12 +2480,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2558,62 +2500,62 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125194278</v>
+        <v>125195016</v>
       </c>
       <c r="B18" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596069</v>
+        <v>596057</v>
       </c>
       <c r="R18" t="n">
-        <v>6925880</v>
+        <v>6925928</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2645,7 +2587,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2655,7 +2597,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2682,15 +2624,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125192314</v>
+        <v>125194517</v>
       </c>
       <c r="B19" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2698,16 +2635,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2723,14 +2660,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596087</v>
+        <v>596060</v>
       </c>
       <c r="R19" t="n">
-        <v>6925836</v>
+        <v>6925896</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2762,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2772,12 +2709,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2792,67 +2724,61 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125193331</v>
+        <v>125194045</v>
       </c>
       <c r="B20" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>595959</v>
+        <v>596078</v>
       </c>
       <c r="R20" t="n">
-        <v>6925918</v>
+        <v>6925853</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2884,7 +2810,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2894,12 +2820,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Kan finnas mer under löven</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2914,67 +2840,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125193611</v>
+        <v>125196036</v>
       </c>
       <c r="B21" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596006</v>
+        <v>596020</v>
       </c>
       <c r="R21" t="n">
-        <v>6925913</v>
+        <v>6925933</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3006,7 +2927,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3016,12 +2937,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3036,66 +2952,62 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125194219</v>
+        <v>125191651</v>
       </c>
       <c r="B22" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>80</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596068</v>
+        <v>596135</v>
       </c>
       <c r="R22" t="n">
-        <v>6925867</v>
+        <v>6925799</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3127,7 +3039,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3137,7 +3049,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3152,66 +3069,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125194410</v>
+        <v>125192270</v>
       </c>
       <c r="B23" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596069</v>
+        <v>596164</v>
       </c>
       <c r="R23" t="n">
-        <v>6925880</v>
+        <v>6925821</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3243,7 +3151,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3253,7 +3161,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3280,15 +3188,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125196940</v>
+        <v>125192972</v>
       </c>
       <c r="B24" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3296,39 +3199,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596026</v>
+        <v>596152</v>
       </c>
       <c r="R24" t="n">
-        <v>6925885</v>
+        <v>6925878</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3360,7 +3263,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3370,7 +3273,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3385,66 +3293,57 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125194116</v>
+        <v>125194278</v>
       </c>
       <c r="B25" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>596053</v>
+        <v>596069</v>
       </c>
       <c r="R25" t="n">
-        <v>6925860</v>
+        <v>6925880</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3476,7 +3375,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3486,7 +3385,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3501,27 +3400,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125193494</v>
+        <v>125194410</v>
       </c>
       <c r="B26" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3548,7 +3442,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3557,10 +3451,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596117</v>
+        <v>596069</v>
       </c>
       <c r="R26" t="n">
-        <v>6925846</v>
+        <v>6925880</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3592,7 +3486,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3602,12 +3496,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>* kan finnas mer under alla löv</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3634,43 +3523,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125195016</v>
+        <v>125194219</v>
       </c>
       <c r="B27" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>80</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3679,10 +3562,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>596057</v>
+        <v>596068</v>
       </c>
       <c r="R27" t="n">
-        <v>6925928</v>
+        <v>6925867</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3714,7 +3597,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3724,7 +3607,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3751,15 +3634,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125195720</v>
+        <v>125193494</v>
       </c>
       <c r="B28" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3786,19 +3664,19 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>9</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596021</v>
+        <v>596117</v>
       </c>
       <c r="R28" t="n">
-        <v>6925959</v>
+        <v>6925846</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3830,7 +3708,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3840,7 +3718,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>* kan finnas mer under alla löv</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3855,67 +3738,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125195512</v>
+        <v>125192037</v>
       </c>
       <c r="B29" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596000</v>
+        <v>596137</v>
       </c>
       <c r="R29" t="n">
-        <v>6925950</v>
+        <v>6925817</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3947,7 +3820,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3957,7 +3830,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3972,27 +3845,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125192466</v>
+        <v>125195720</v>
       </c>
       <c r="B30" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4019,19 +3887,19 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>596169</v>
+        <v>596021</v>
       </c>
       <c r="R30" t="n">
-        <v>6925853</v>
+        <v>6925959</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4063,7 +3931,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4073,12 +3941,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:01</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>10x</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4093,27 +3956,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125192972</v>
+        <v>125194304</v>
       </c>
       <c r="B31" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4146,14 +4004,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596152</v>
+        <v>596074</v>
       </c>
       <c r="R31" t="n">
-        <v>6925878</v>
+        <v>6925862</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4185,7 +4043,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4195,12 +4053,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4215,66 +4073,62 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125195800</v>
+        <v>125195512</v>
       </c>
       <c r="B32" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596030</v>
+        <v>596000</v>
       </c>
       <c r="R32" t="n">
-        <v>6925941</v>
+        <v>6925950</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4306,7 +4160,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4316,7 +4170,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4331,12 +4185,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -1592,54 +1592,50 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125191639</v>
+        <v>125196940</v>
       </c>
       <c r="B10" t="n">
-        <v>56843</v>
+        <v>57811</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596138</v>
+        <v>596026</v>
       </c>
       <c r="R10" t="n">
-        <v>6925797</v>
+        <v>6925885</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,12 +1677,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Myllgrop av tjäder + fjäder</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,62 +1692,57 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125196940</v>
+        <v>125193908</v>
       </c>
       <c r="B11" t="n">
-        <v>57811</v>
+        <v>105348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596026</v>
+        <v>596085</v>
       </c>
       <c r="R11" t="n">
-        <v>6925885</v>
+        <v>6925872</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1788,7 +1774,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1798,7 +1784,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,22 +1799,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125193908</v>
+        <v>125191639</v>
       </c>
       <c r="B12" t="n">
-        <v>105348</v>
+        <v>56843</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1836,34 +1822,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596085</v>
+        <v>596138</v>
       </c>
       <c r="R12" t="n">
-        <v>6925872</v>
+        <v>6925797</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1900,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Myllgrop av tjäder + fjäder</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125192424</v>
+        <v>125194492</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>98331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596087</v>
+        <v>596063</v>
       </c>
       <c r="R2" t="n">
-        <v>6925836</v>
+        <v>6925899</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194492</v>
+        <v>125194116</v>
       </c>
       <c r="B3" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -831,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596063</v>
+        <v>596053</v>
       </c>
       <c r="R3" t="n">
-        <v>6925899</v>
+        <v>6925860</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +870,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,37 +897,38 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125194116</v>
+        <v>125192424</v>
       </c>
       <c r="B4" t="n">
-        <v>98324</v>
+        <v>57651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -942,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596053</v>
+        <v>596087</v>
       </c>
       <c r="R4" t="n">
-        <v>6925860</v>
+        <v>6925836</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +982,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1368,7 +1368,7 @@
         <v>125195800</v>
       </c>
       <c r="B8" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>125192466</v>
       </c>
       <c r="B9" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1592,50 +1592,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125196940</v>
+        <v>125191639</v>
       </c>
       <c r="B10" t="n">
-        <v>57811</v>
+        <v>56843</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596026</v>
+        <v>596138</v>
       </c>
       <c r="R10" t="n">
-        <v>6925885</v>
+        <v>6925797</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1667,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1677,7 +1681,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Myllgrop av tjäder + fjäder</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1692,12 +1701,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1707,7 +1716,7 @@
         <v>125193908</v>
       </c>
       <c r="B11" t="n">
-        <v>105348</v>
+        <v>105355</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1811,54 +1820,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125191639</v>
+        <v>125196940</v>
       </c>
       <c r="B12" t="n">
-        <v>56843</v>
+        <v>57811</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596138</v>
+        <v>596026</v>
       </c>
       <c r="R12" t="n">
-        <v>6925797</v>
+        <v>6925885</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1890,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,12 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Myllgrop av tjäder + fjäder</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,57 +1920,62 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125192112</v>
+        <v>125193041</v>
       </c>
       <c r="B13" t="n">
-        <v>43933</v>
+        <v>57651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>101735</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>596164</v>
+        <v>595982</v>
       </c>
       <c r="R13" t="n">
-        <v>6925821</v>
+        <v>6925883</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2002,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,12 +2017,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
+          <t>Ringhack på tall.  Väldigt många.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,19 +2037,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125193041</v>
+        <v>125193970</v>
       </c>
       <c r="B14" t="n">
         <v>57651</v>
@@ -2084,10 +2089,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>595982</v>
+        <v>596053</v>
       </c>
       <c r="R14" t="n">
-        <v>6925883</v>
+        <v>6925860</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2119,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,12 +2134,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Väldigt många.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,50 +2166,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125193970</v>
+        <v>125192112</v>
       </c>
       <c r="B15" t="n">
-        <v>57651</v>
+        <v>43933</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>101735</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596053</v>
+        <v>596164</v>
       </c>
       <c r="R15" t="n">
-        <v>6925860</v>
+        <v>6925821</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2266,22 +2266,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125194671</v>
+        <v>125195016</v>
       </c>
       <c r="B16" t="n">
-        <v>57651</v>
+        <v>57648</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,16 +2289,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596069</v>
+        <v>596057</v>
       </c>
       <c r="R16" t="n">
-        <v>6925880</v>
+        <v>6925928</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2363,12 +2363,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall.</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,7 +2390,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125191997</v>
+        <v>125194671</v>
       </c>
       <c r="B17" t="n">
         <v>57651</v>
@@ -2435,10 +2430,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>596164</v>
+        <v>596069</v>
       </c>
       <c r="R17" t="n">
-        <v>6925821</v>
+        <v>6925880</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2470,7 +2465,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2480,12 +2475,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
+          <t>Ringhack av tretåig hackspett på Tall.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2512,10 +2507,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125195016</v>
+        <v>125191997</v>
       </c>
       <c r="B18" t="n">
-        <v>57648</v>
+        <v>57651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2523,16 +2518,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2552,10 +2547,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596057</v>
+        <v>596164</v>
       </c>
       <c r="R18" t="n">
-        <v>6925928</v>
+        <v>6925821</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2587,7 +2582,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2597,7 +2592,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2739,7 +2739,7 @@
         <v>125194045</v>
       </c>
       <c r="B20" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3305,35 +3305,39 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125194278</v>
+        <v>125194410</v>
       </c>
       <c r="B25" t="n">
-        <v>97202</v>
+        <v>98331</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
@@ -3375,7 +3379,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3385,7 +3389,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3412,39 +3416,35 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125194410</v>
+        <v>125194278</v>
       </c>
       <c r="B26" t="n">
-        <v>98324</v>
+        <v>97209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3526,7 +3526,7 @@
         <v>125194219</v>
       </c>
       <c r="B27" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>125193494</v>
       </c>
       <c r="B28" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>125192037</v>
       </c>
       <c r="B29" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>125195720</v>
       </c>
       <c r="B30" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125194492</v>
+        <v>125192424</v>
       </c>
       <c r="B2" t="n">
-        <v>98331</v>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -714,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596063</v>
+        <v>596087</v>
       </c>
       <c r="R2" t="n">
-        <v>6925899</v>
+        <v>6925836</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -759,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194116</v>
+        <v>125194492</v>
       </c>
       <c r="B3" t="n">
         <v>98331</v>
@@ -816,7 +822,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596053</v>
+        <v>596063</v>
       </c>
       <c r="R3" t="n">
-        <v>6925860</v>
+        <v>6925899</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,38 +903,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125192424</v>
+        <v>125194116</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>98331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>60</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -937,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596087</v>
+        <v>596053</v>
       </c>
       <c r="R4" t="n">
-        <v>6925836</v>
+        <v>6925860</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,12 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1131,38 +1131,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125192021</v>
+        <v>125195800</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>98331</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1171,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596137</v>
+        <v>596030</v>
       </c>
       <c r="R6" t="n">
-        <v>6925817</v>
+        <v>6925941</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,7 +1205,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,12 +1215,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:42</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,7 +1242,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125193331</v>
+        <v>125192021</v>
       </c>
       <c r="B7" t="n">
         <v>57651</v>
@@ -1288,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>595959</v>
+        <v>596137</v>
       </c>
       <c r="R7" t="n">
-        <v>6925918</v>
+        <v>6925817</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1333,12 +1327,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,37 +1359,38 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125195800</v>
+        <v>125193331</v>
       </c>
       <c r="B8" t="n">
-        <v>98331</v>
+        <v>57651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1404,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>596030</v>
+        <v>595959</v>
       </c>
       <c r="R8" t="n">
-        <v>6925941</v>
+        <v>6925918</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1439,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,7 +1444,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2964,10 +2964,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125191651</v>
+        <v>125192270</v>
       </c>
       <c r="B22" t="n">
-        <v>57651</v>
+        <v>80070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,39 +2975,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596135</v>
+        <v>596164</v>
       </c>
       <c r="R22" t="n">
-        <v>6925799</v>
+        <v>6925821</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3039,7 +3034,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3049,12 +3044,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:29</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3069,22 +3059,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125192270</v>
+        <v>125191651</v>
       </c>
       <c r="B23" t="n">
-        <v>80070</v>
+        <v>57651</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3092,34 +3082,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596164</v>
+        <v>596135</v>
       </c>
       <c r="R23" t="n">
-        <v>6925821</v>
+        <v>6925799</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3151,7 +3146,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3161,7 +3156,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3176,12 +3176,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3305,39 +3305,35 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125194410</v>
+        <v>125194278</v>
       </c>
       <c r="B25" t="n">
-        <v>98331</v>
+        <v>97209</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
@@ -3379,7 +3375,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3389,7 +3385,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3416,35 +3412,39 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125194278</v>
+        <v>125194410</v>
       </c>
       <c r="B26" t="n">
-        <v>97209</v>
+        <v>98331</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -2281,7 +2281,7 @@
         <v>125195016</v>
       </c>
       <c r="B16" t="n">
-        <v>57648</v>
+        <v>57658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>125194517</v>
       </c>
       <c r="B19" t="n">
-        <v>57648</v>
+        <v>57658</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -2281,7 +2281,7 @@
         <v>125195016</v>
       </c>
       <c r="B16" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>125194517</v>
       </c>
       <c r="B19" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -2281,7 +2281,7 @@
         <v>125195016</v>
       </c>
       <c r="B16" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>125194517</v>
       </c>
       <c r="B19" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -2281,7 +2281,7 @@
         <v>125195016</v>
       </c>
       <c r="B16" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>125194517</v>
       </c>
       <c r="B19" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -2281,7 +2281,7 @@
         <v>125195016</v>
       </c>
       <c r="B16" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>125194517</v>
       </c>
       <c r="B19" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -2281,7 +2281,7 @@
         <v>125195016</v>
       </c>
       <c r="B16" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>125194517</v>
       </c>
       <c r="B19" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125192424</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>125193611</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>125192021</v>
       </c>
       <c r="B7" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125193331</v>
       </c>
       <c r="B8" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>125193041</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>125193970</v>
       </c>
       <c r="B14" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>125194671</v>
       </c>
       <c r="B17" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>125191997</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>125191651</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>125192972</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>125194304</v>
       </c>
       <c r="B31" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125192424</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>125193611</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>125192021</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125193331</v>
       </c>
       <c r="B8" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>125193041</v>
       </c>
       <c r="B13" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>125193970</v>
       </c>
       <c r="B14" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>125194671</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>125191997</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>125191651</v>
       </c>
       <c r="B23" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3191,7 +3191,7 @@
         <v>125192972</v>
       </c>
       <c r="B24" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
         <v>125194304</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125192424</v>
+        <v>125192037</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>596087</v>
+        <v>596137</v>
       </c>
       <c r="R2" t="n">
-        <v>6925836</v>
+        <v>6925817</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:59</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,52 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194492</v>
+        <v>125689173</v>
       </c>
       <c r="B3" t="n">
-        <v>98331</v>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1205</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Öster-Svarttjärnsberget, Öster-Svarttjärnsberget, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>596063</v>
+        <v>595984</v>
       </c>
       <c r="R3" t="n">
-        <v>6925899</v>
+        <v>6925977</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:07</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:07</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,61 +867,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125194116</v>
+        <v>125192270</v>
       </c>
       <c r="B4" t="n">
-        <v>98331</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>596053</v>
+        <v>596164</v>
       </c>
       <c r="R4" t="n">
-        <v>6925860</v>
+        <v>6925821</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +949,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +959,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,39 +974,39 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125193611</v>
+        <v>125194517</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1050,14 +1022,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>596006</v>
+        <v>596060</v>
       </c>
       <c r="R5" t="n">
-        <v>6925913</v>
+        <v>6925896</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1061,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,12 +1071,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,61 +1086,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125195800</v>
+        <v>125195016</v>
       </c>
       <c r="B6" t="n">
-        <v>98331</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>35</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>596030</v>
+        <v>596057</v>
       </c>
       <c r="R6" t="n">
-        <v>6925941</v>
+        <v>6925928</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1215,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,22 +1198,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125192021</v>
+        <v>125191651</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1282,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>596137</v>
+        <v>596135</v>
       </c>
       <c r="R7" t="n">
-        <v>6925817</v>
+        <v>6925799</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,12 +1295,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125193331</v>
+        <v>125191997</v>
       </c>
       <c r="B8" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,14 +1363,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>595959</v>
+        <v>596164</v>
       </c>
       <c r="R8" t="n">
-        <v>6925918</v>
+        <v>6925821</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1434,7 +1402,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,12 +1412,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,61 +1432,62 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125192466</v>
+        <v>125192021</v>
       </c>
       <c r="B9" t="n">
-        <v>98331</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>596169</v>
+        <v>596137</v>
       </c>
       <c r="R9" t="n">
-        <v>6925853</v>
+        <v>6925817</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1550,7 +1519,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1560,12 +1529,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>10x</t>
+          <t>Ringhack på tall. Fortfarande lite kåda kvar varför jag rapporterar dom som färska.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1580,51 +1549,47 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125191639</v>
+        <v>125192314</v>
       </c>
       <c r="B10" t="n">
-        <v>56843</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1632,14 +1597,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>596138</v>
+        <v>596087</v>
       </c>
       <c r="R10" t="n">
-        <v>6925797</v>
+        <v>6925836</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1636,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,12 +1646,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Myllgrop av tjäder + fjäder</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,57 +1666,62 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125193908</v>
+        <v>125192972</v>
       </c>
       <c r="B11" t="n">
-        <v>105355</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>596085</v>
+        <v>596152</v>
       </c>
       <c r="R11" t="n">
-        <v>6925872</v>
+        <v>6925878</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1763,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125196940</v>
+        <v>125193041</v>
       </c>
       <c r="B12" t="n">
-        <v>57811</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1831,27 +1806,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1860,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>596026</v>
+        <v>595982</v>
       </c>
       <c r="R12" t="n">
-        <v>6925885</v>
+        <v>6925883</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1880,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.  Väldigt många.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125193041</v>
+        <v>125193331</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>595982</v>
+        <v>595959</v>
       </c>
       <c r="R13" t="n">
-        <v>6925883</v>
+        <v>6925918</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,12 +1997,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack på tall.  Väldigt många.</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125193970</v>
+        <v>125193611</v>
       </c>
       <c r="B14" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>596053</v>
+        <v>596006</v>
       </c>
       <c r="R14" t="n">
-        <v>6925860</v>
+        <v>6925913</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2124,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2166,45 +2146,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125192112</v>
+        <v>125193970</v>
       </c>
       <c r="B15" t="n">
-        <v>43933</v>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>101735</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>596164</v>
+        <v>596053</v>
       </c>
       <c r="R15" t="n">
-        <v>6925821</v>
+        <v>6925860</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2236,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,12 +2231,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2266,22 +2251,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125195016</v>
+        <v>125194304</v>
       </c>
       <c r="B16" t="n">
-        <v>57681</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,16 +2274,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2314,14 +2299,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>596057</v>
+        <v>596074</v>
       </c>
       <c r="R16" t="n">
-        <v>6925928</v>
+        <v>6925862</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2353,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2363,7 +2348,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2378,12 +2368,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2393,7 +2383,7 @@
         <v>125194671</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2507,35 +2497,39 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125191997</v>
+        <v>125191639</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>57141</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -2547,10 +2541,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>596164</v>
+        <v>596138</v>
       </c>
       <c r="R18" t="n">
-        <v>6925821</v>
+        <v>6925797</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2582,7 +2576,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2592,12 +2586,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall, både färska och äldre spår</t>
+          <t>Myllgrop av tjäder + fjäder</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2624,50 +2618,50 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125194517</v>
+        <v>125195512</v>
       </c>
       <c r="B19" t="n">
-        <v>57681</v>
+        <v>57141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>596060</v>
+        <v>596000</v>
       </c>
       <c r="R19" t="n">
-        <v>6925896</v>
+        <v>6925950</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2699,7 +2693,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2709,7 +2703,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,49 +2730,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125194045</v>
+        <v>125196036</v>
       </c>
       <c r="B20" t="n">
-        <v>98331</v>
+        <v>57141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Östersvartjärn.., Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>596078</v>
+        <v>596020</v>
       </c>
       <c r="R20" t="n">
-        <v>6925853</v>
+        <v>6925933</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2810,7 +2805,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2820,12 +2815,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Kan finnas mer under löven</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,10 +2842,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125196036</v>
+        <v>125192112</v>
       </c>
       <c r="B21" t="n">
-        <v>56843</v>
+        <v>44177</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,39 +2853,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>101735</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>596020</v>
+        <v>596164</v>
       </c>
       <c r="R21" t="n">
-        <v>6925933</v>
+        <v>6925821</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2927,7 +2912,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2937,7 +2922,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:54</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Flertal exemplar ( hål )  Pinnen går djupt ner i veden</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2964,10 +2954,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125192270</v>
+        <v>125196940</v>
       </c>
       <c r="B22" t="n">
-        <v>80070</v>
+        <v>58114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2975,34 +2965,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>596164</v>
+        <v>596026</v>
       </c>
       <c r="R22" t="n">
-        <v>6925821</v>
+        <v>6925885</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3034,7 +3029,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3044,7 +3039,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3059,62 +3054,61 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125191651</v>
+        <v>125192466</v>
       </c>
       <c r="B23" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Öster-svarttjärn, Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>596135</v>
+        <v>596169</v>
       </c>
       <c r="R23" t="n">
-        <v>6925799</v>
+        <v>6925853</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3146,7 +3140,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3156,12 +3150,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>10x</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3176,50 +3170,49 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125192972</v>
+        <v>125193494</v>
       </c>
       <c r="B24" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3228,10 +3221,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>596152</v>
+        <v>596117</v>
       </c>
       <c r="R24" t="n">
-        <v>6925878</v>
+        <v>6925846</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3263,7 +3256,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3273,12 +3266,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Många ringhack av tretåig hackspett på Tall, både äldre och färska spår.</t>
+          <t>* kan finnas mer under alla löv</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3305,45 +3298,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125194278</v>
+        <v>125194045</v>
       </c>
       <c r="B25" t="n">
-        <v>97209</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>596069</v>
+        <v>596078</v>
       </c>
       <c r="R25" t="n">
-        <v>6925880</v>
+        <v>6925853</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3375,7 +3372,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3385,7 +3382,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Kan finnas mer under löven</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3412,10 +3414,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125194410</v>
+        <v>125194116</v>
       </c>
       <c r="B26" t="n">
-        <v>98331</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3442,19 +3444,19 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Östersvartjärn., Mpd</t>
+          <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>596069</v>
+        <v>596053</v>
       </c>
       <c r="R26" t="n">
-        <v>6925880</v>
+        <v>6925860</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3486,7 +3488,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3496,7 +3498,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3511,12 +3513,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3526,7 +3528,7 @@
         <v>125194219</v>
       </c>
       <c r="B27" t="n">
-        <v>98331</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3634,10 +3636,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125193494</v>
+        <v>125194410</v>
       </c>
       <c r="B28" t="n">
-        <v>98331</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3664,7 +3666,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3673,10 +3675,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>596117</v>
+        <v>596069</v>
       </c>
       <c r="R28" t="n">
-        <v>6925846</v>
+        <v>6925880</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3708,7 +3710,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3718,12 +3720,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:31</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>* kan finnas mer under alla löv</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3750,45 +3747,49 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125192037</v>
+        <v>125194492</v>
       </c>
       <c r="B29" t="n">
-        <v>91227</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Öster-svarttjärn, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>596137</v>
+        <v>596063</v>
       </c>
       <c r="R29" t="n">
-        <v>6925817</v>
+        <v>6925899</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3820,7 +3821,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3830,7 +3831,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3860,7 +3861,7 @@
         <v>125195720</v>
       </c>
       <c r="B30" t="n">
-        <v>98331</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3968,38 +3969,37 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125194304</v>
+        <v>125195800</v>
       </c>
       <c r="B31" t="n">
-        <v>57741</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4008,10 +4008,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>596074</v>
+        <v>596030</v>
       </c>
       <c r="R31" t="n">
-        <v>6925862</v>
+        <v>6925941</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4053,12 +4053,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4085,10 +4080,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125195512</v>
+        <v>125193908</v>
       </c>
       <c r="B32" t="n">
-        <v>56843</v>
+        <v>106244</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4096,39 +4091,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Östersvartjärn.., Mpd</t>
+          <t>Östersvartjärn., Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>596000</v>
+        <v>596085</v>
       </c>
       <c r="R32" t="n">
-        <v>6925950</v>
+        <v>6925872</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4160,7 +4150,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4170,7 +4160,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4194,6 +4184,113 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125194278</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Östersvartjärn., Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>596069</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6925880</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45976-2024 artfynd.xlsx
+++ b/artfynd/A 45976-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125689173</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125193041</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125193331</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125193611</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195512</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1344,6 +1374,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125196036</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1456,6 +1491,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125196940</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1567,6 +1607,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195720</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1678,6 +1723,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195800</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1785,6 +1835,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125192037</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1892,6 +1947,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125192270</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125194517</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2116,6 +2181,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125195016</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2233,6 +2303,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125191651</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2350,6 +2425,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125191997</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2467,6 +2547,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125192021</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2584,6 +2669,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125192314</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2701,6 +2791,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125192972</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2818,6 +2913,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125193970</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2935,6 +3035,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125194304</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3052,6 +3157,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125194671</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3173,6 +3283,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125191639</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3285,6 +3400,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125192112</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3401,6 +3521,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125192466</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3517,6 +3642,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125193494</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3633,6 +3763,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125194045</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3744,6 +3879,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125194116</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3855,6 +3995,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125194219</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3966,6 +4111,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125194410</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4077,6 +4227,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125194492</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4184,6 +4339,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125193908</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4291,8 +4451,47 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125194278</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>